--- a/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ30"/>
+  <dimension ref="A1:AQ36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0624</v>
+        <v>0.0823</v>
       </c>
       <c r="E2">
-        <v>0.1485</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="G2">
-        <v>0.3025978369940908</v>
+        <v>0.3792546248368367</v>
       </c>
       <c r="H2">
-        <v>0.3025978369940908</v>
+        <v>0.3792546248368367</v>
       </c>
       <c r="I2">
-        <v>0.3425855725275951</v>
+        <v>0.284160777782779</v>
       </c>
       <c r="J2">
-        <v>0.2549161701288274</v>
+        <v>0.2130702221822675</v>
       </c>
       <c r="K2">
-        <v>40.976</v>
+        <v>44.202</v>
       </c>
       <c r="L2">
-        <v>0.2284312632400491</v>
+        <v>0.1989557546023316</v>
       </c>
       <c r="M2">
-        <v>20.7</v>
+        <v>20.846</v>
       </c>
       <c r="N2">
-        <v>0.02061342362079267</v>
+        <v>0.03033027789902517</v>
       </c>
       <c r="O2">
-        <v>0.5051737602499023</v>
+        <v>0.4716076195647256</v>
       </c>
       <c r="P2">
-        <v>20.7</v>
+        <v>20.846</v>
       </c>
       <c r="Q2">
-        <v>0.02061342362079267</v>
+        <v>0.03033027789902517</v>
       </c>
       <c r="R2">
-        <v>0.5051737602499023</v>
+        <v>0.4716076195647256</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>178.451</v>
+        <v>232.56</v>
       </c>
       <c r="V2">
-        <v>0.1777046405098586</v>
+        <v>0.3383675250982104</v>
       </c>
       <c r="W2">
-        <v>0.1309729637050219</v>
+        <v>0.09127033492822967</v>
       </c>
       <c r="X2">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y2">
-        <v>0.05399718606137567</v>
+        <v>-0.0315031104784514</v>
       </c>
       <c r="Z2">
-        <v>1.193757694739294</v>
+        <v>0.943873974534903</v>
       </c>
       <c r="AA2">
-        <v>0.3162258093249267</v>
+        <v>0.2427919072649095</v>
       </c>
       <c r="AB2">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC2">
-        <v>0.2392423264326917</v>
+        <v>0.1200184618582284</v>
       </c>
       <c r="AD2">
-        <v>1.656</v>
+        <v>1.922</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.656</v>
+        <v>1.922</v>
       </c>
       <c r="AG2">
-        <v>-176.795</v>
+        <v>-230.638</v>
       </c>
       <c r="AH2">
-        <v>0.001646358922151879</v>
+        <v>0.002788651552039836</v>
       </c>
       <c r="AI2">
-        <v>0.004484815001381193</v>
+        <v>0.004420707865271912</v>
       </c>
       <c r="AJ2">
-        <v>-0.2136740773865277</v>
+        <v>-0.5050518764425331</v>
       </c>
       <c r="AK2">
-        <v>-0.9266228150632878</v>
+        <v>-1.140575237869167</v>
       </c>
       <c r="AL2">
-        <v>0.843</v>
+        <v>0.6669999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.843</v>
+        <v>0.6669999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.02541202467544425</v>
+        <v>0.02888357903911756</v>
       </c>
       <c r="AO2">
-        <v>72.89798339264532</v>
+        <v>94.65067466266868</v>
       </c>
       <c r="AP2">
-        <v>-2.712994506337661</v>
+        <v>-3.465999428940685</v>
       </c>
       <c r="AQ2">
-        <v>72.89798339264532</v>
+        <v>94.65067466266868</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sena Kalyan Insurance Company Limited (DSE:SKICL)</t>
+          <t>Provati Insurance Company Limited (DSE:PROVATIINS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,77 +721,92 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.19</v>
+      </c>
+      <c r="E3">
+        <v>0.14</v>
+      </c>
       <c r="G3">
-        <v>0.3053097345132744</v>
+        <v>0.2198019801980198</v>
       </c>
       <c r="H3">
-        <v>0.3053097345132744</v>
+        <v>0.2198019801980198</v>
       </c>
       <c r="I3">
-        <v>0.2986725663716814</v>
+        <v>0.1178217821782178</v>
       </c>
       <c r="J3">
-        <v>0.2466814159292036</v>
+        <v>0.09789026402640263</v>
       </c>
       <c r="K3">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0.2455752212389381</v>
+        <v>0.09900990099009901</v>
       </c>
       <c r="M3">
-        <v>0.283</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.007817679558011048</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.2549549549549549</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.283</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.007817679558011048</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2549549549549549</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>7.61</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.3294372294372294</v>
+      </c>
+      <c r="W3">
+        <v>0.1164144353899884</v>
       </c>
       <c r="X3">
-        <v>0.07697577764364623</v>
+        <v>0.1246334026942277</v>
+      </c>
+      <c r="Y3">
+        <v>-0.008218967304239391</v>
       </c>
       <c r="AB3">
-        <v>0.07697577764364623</v>
+        <v>0.1227968620151247</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.758</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.758</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-6.852</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0317713136054992</v>
+      </c>
+      <c r="AI3">
+        <v>0.08857209628417854</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.4217134416543574</v>
+      </c>
+      <c r="AK3">
+        <v>-7.227848101265827</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -800,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.5742424242424242</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-5.19090909090909</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sonar Bangla Insurance Limited (DSE:SONARBAINS)</t>
+          <t>Bangladesh National Insurance Company Limited (DSE:BNICL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -823,64 +838,67 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0542</v>
+        <v>0.161</v>
       </c>
       <c r="E4">
-        <v>0.07769999999999999</v>
+        <v>0.191</v>
       </c>
       <c r="G4">
-        <v>0.3793814432989691</v>
+        <v>0.2410986775178026</v>
       </c>
       <c r="H4">
-        <v>0.3793814432989691</v>
+        <v>0.2410986775178026</v>
       </c>
       <c r="I4">
-        <v>0.3608247422680413</v>
+        <v>0.202441505595117</v>
       </c>
       <c r="J4">
-        <v>0.25475096261334</v>
+        <v>0.1660429318618535</v>
       </c>
       <c r="K4">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="L4">
-        <v>0.2329896907216495</v>
+        <v>0.1648016276703967</v>
       </c>
       <c r="M4">
-        <v>0.473</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.01359195402298851</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4185840707964602</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.473</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.01359195402298851</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.4185840707964602</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.642570281124498</v>
+      </c>
+      <c r="W4">
+        <v>0.1572815533980582</v>
       </c>
       <c r="X4">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="Y4">
+        <v>0.03450810799137717</v>
       </c>
       <c r="AB4">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -892,31 +910,37 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-1.797752808988764</v>
+      </c>
+      <c r="AK4">
+        <v>3.478260869565218</v>
       </c>
       <c r="AL4">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AM4">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>159.0909090909091</v>
+        <v>153.0769230769231</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>-7.476635514018692</v>
       </c>
       <c r="AQ4">
-        <v>159.0909090909091</v>
+        <v>153.0769230769231</v>
       </c>
     </row>
     <row r="5">
@@ -927,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Federal Insurance Company Limited (DSE:FEDERALINS)</t>
+          <t>Sena Kalyan Insurance Company Limited (DSE:SKICL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -935,86 +959,77 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.0624</v>
-      </c>
-      <c r="E5">
-        <v>0.645</v>
-      </c>
       <c r="G5">
-        <v>0.2812500000000001</v>
+        <v>0.3425925925925926</v>
       </c>
       <c r="H5">
-        <v>0.2812500000000001</v>
+        <v>0.3425925925925926</v>
       </c>
       <c r="I5">
-        <v>0.2899305555555556</v>
+        <v>0.3287037037037037</v>
       </c>
       <c r="J5">
-        <v>0.2013888888888889</v>
+        <v>0.3008718572587185</v>
       </c>
       <c r="K5">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="L5">
-        <v>0.2013888888888889</v>
+        <v>0.2893518518518519</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.184</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.008214285714285714</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1472</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.184</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.008214285714285714</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.1472</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.1697986577181208</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>0.07783913161492904</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AB5">
-        <v>0.07706366907237849</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AD5">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-4.444</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.02025249868490268</v>
-      </c>
-      <c r="AI5">
-        <v>0.0564309270795163</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.1752642372613977</v>
-      </c>
-      <c r="AK5">
-        <v>-0.758879781420765</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1023,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.3294117647058823</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-2.376470588235294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1037,7 +1052,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phoenix Insurance Company Limited (DSE:PHENIXINS)</t>
+          <t>Sonar Bangla Insurance Limited (DSE:SONARBAINS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1046,46 +1061,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0533</v>
+        <v>0.109</v>
       </c>
       <c r="E6">
-        <v>-0.0104</v>
+        <v>0.0852</v>
       </c>
       <c r="G6">
-        <v>0.2480376766091052</v>
+        <v>0.2596439169139466</v>
       </c>
       <c r="H6">
-        <v>0.2480376766091052</v>
+        <v>0.2596439169139466</v>
       </c>
       <c r="I6">
-        <v>0.2919937205651492</v>
+        <v>0.2477744807121662</v>
       </c>
       <c r="J6">
-        <v>0.2200212143069286</v>
+        <v>0.1974151219700181</v>
       </c>
       <c r="K6">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="L6">
-        <v>0.2182103610675039</v>
+        <v>0.1750741839762611</v>
       </c>
       <c r="M6">
-        <v>1.22</v>
+        <v>0.722</v>
       </c>
       <c r="N6">
-        <v>0.0431095406360424</v>
+        <v>0.03902702702702703</v>
       </c>
       <c r="O6">
-        <v>0.8776978417266188</v>
+        <v>0.611864406779661</v>
       </c>
       <c r="P6">
-        <v>1.22</v>
+        <v>0.722</v>
       </c>
       <c r="Q6">
-        <v>0.0431095406360424</v>
+        <v>0.03902702702702703</v>
       </c>
       <c r="R6">
-        <v>0.8776978417266188</v>
+        <v>0.611864406779661</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1094,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.1848056537102473</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AB6">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1115,19 +1130,13 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-5.23</v>
+        <v>0</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
       <c r="AJ6">
-        <v>-0.2267013437364543</v>
-      </c>
-      <c r="AK6">
-        <v>-0.3565098841172462</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1139,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>-2.615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1150,7 +1159,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agrani Insurance Company Limited (DSE:AGRANINS)</t>
+          <t>Mercantile Insurance Company Limited (DSE:MERCINS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1158,47 +1167,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0373</v>
-      </c>
-      <c r="E7">
-        <v>0.0843</v>
-      </c>
       <c r="G7">
-        <v>0.34375</v>
+        <v>0.3245033112582781</v>
       </c>
       <c r="H7">
-        <v>0.34375</v>
+        <v>0.3245033112582781</v>
       </c>
       <c r="I7">
-        <v>0.35</v>
+        <v>0.2869757174392936</v>
       </c>
       <c r="J7">
-        <v>0.2552752293577982</v>
+        <v>0.2155707357772331</v>
       </c>
       <c r="K7">
-        <v>0.794</v>
+        <v>0.949</v>
       </c>
       <c r="L7">
-        <v>0.248125</v>
+        <v>0.2094922737306843</v>
       </c>
       <c r="M7">
-        <v>0.468</v>
+        <v>0.428</v>
       </c>
       <c r="N7">
-        <v>0.02098654708520179</v>
+        <v>0.0334375</v>
       </c>
       <c r="O7">
-        <v>0.5894206549118388</v>
+        <v>0.4510010537407798</v>
       </c>
       <c r="P7">
-        <v>0.468</v>
+        <v>0.428</v>
       </c>
       <c r="Q7">
-        <v>0.02098654708520179</v>
+        <v>0.0334375</v>
       </c>
       <c r="R7">
-        <v>0.5894206549118388</v>
+        <v>0.4510010537407798</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1207,58 +1210,58 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3.2</v>
+        <v>11.1</v>
       </c>
       <c r="V7">
-        <v>0.1434977578475336</v>
+        <v>0.8671874999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.09743326488706365</v>
       </c>
       <c r="X7">
-        <v>0.07770059827211985</v>
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="Y7">
+        <v>-0.02534018051961742</v>
       </c>
       <c r="AB7">
-        <v>0.07704980663047348</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AD7">
-        <v>0.387</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.387</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>-2.813</v>
+        <v>-11.1</v>
       </c>
       <c r="AH7">
-        <v>0.01705822717856041</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.05392225163717431</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.1443526453533125</v>
+        <v>-6.529411764705878</v>
       </c>
       <c r="AK7">
-        <v>-0.7073170731707318</v>
+        <v>4.911504424778761</v>
       </c>
       <c r="AL7">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>0.3365217391304348</v>
-      </c>
-      <c r="AO7">
-        <v>20.74074074074074</v>
+        <v>0</v>
       </c>
       <c r="AP7">
-        <v>-2.446086956521739</v>
-      </c>
-      <c r="AQ7">
-        <v>20.74074074074074</v>
+        <v>-8.161764705882351</v>
       </c>
     </row>
     <row r="8">
@@ -1269,7 +1272,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Desh General Insurance Company Limited (DSE:DGIC)</t>
+          <t>Islami Commercial Insurance Company Limited (DSE:ICICL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1277,47 +1280,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>-0.0588</v>
-      </c>
-      <c r="E8">
-        <v>0.261</v>
-      </c>
       <c r="G8">
-        <v>0.3065015479876161</v>
+        <v>0.2228235294117647</v>
       </c>
       <c r="H8">
-        <v>0.3065015479876161</v>
+        <v>0.2228235294117647</v>
       </c>
       <c r="I8">
-        <v>0.2702786377708978</v>
+        <v>0.2447058823529412</v>
       </c>
       <c r="J8">
-        <v>0.1538287991568408</v>
+        <v>0.163929183323815</v>
       </c>
       <c r="K8">
-        <v>0.428</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L8">
-        <v>0.1325077399380805</v>
+        <v>0.1625882352941176</v>
       </c>
       <c r="M8">
-        <v>0.34</v>
+        <v>0.553</v>
       </c>
       <c r="N8">
-        <v>0.01770833333333334</v>
+        <v>0.04007246376811594</v>
       </c>
       <c r="O8">
-        <v>0.7943925233644861</v>
+        <v>0.800289435600579</v>
       </c>
       <c r="P8">
-        <v>0.34</v>
+        <v>0.553</v>
       </c>
       <c r="Q8">
-        <v>0.01770833333333334</v>
+        <v>0.04007246376811594</v>
       </c>
       <c r="R8">
-        <v>0.7943925233644861</v>
+        <v>0.800289435600579</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1326,16 +1323,16 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>0.2789855072463768</v>
       </c>
       <c r="X8">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AB8">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1347,31 +1344,31 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>-0.3869346733668341</v>
+      </c>
+      <c r="AK8">
+        <v>-1.332179930795848</v>
       </c>
       <c r="AL8">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AN8">
         <v>0</v>
       </c>
-      <c r="AO8">
-        <v>8.818181818181818</v>
-      </c>
       <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>8.818181818181818</v>
+        <v>-3.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1382,7 +1379,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Takaful Islami Insurance Limited (DSE:TAKAFULINS)</t>
+          <t>Standard Insurance Limited (DSE:STANDARINS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1391,46 +1388,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.175</v>
+        <v>0.225</v>
       </c>
       <c r="E9">
-        <v>0.164</v>
+        <v>0.0934</v>
       </c>
       <c r="G9">
-        <v>0.1782729805013928</v>
+        <v>0.3674321503131524</v>
       </c>
       <c r="H9">
-        <v>0.1782729805013928</v>
+        <v>0.3674321503131524</v>
       </c>
       <c r="I9">
-        <v>0.2200557103064067</v>
+        <v>0.2881002087682672</v>
       </c>
       <c r="J9">
-        <v>0.161755236407047</v>
+        <v>0.2341080955694734</v>
       </c>
       <c r="K9">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="L9">
-        <v>0.1573816155988858</v>
+        <v>0.2275574112734864</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0.551</v>
       </c>
       <c r="N9">
-        <v>0.03584229390681004</v>
+        <v>0.02727722772277228</v>
       </c>
       <c r="O9">
-        <v>0.8849557522123894</v>
+        <v>0.5055045871559634</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0.551</v>
       </c>
       <c r="Q9">
-        <v>0.03584229390681004</v>
+        <v>0.02727722772277228</v>
       </c>
       <c r="R9">
-        <v>0.8849557522123894</v>
+        <v>0.5055045871559634</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1439,67 +1436,64 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>8.83</v>
+        <v>11.2</v>
       </c>
       <c r="V9">
-        <v>0.3164874551971326</v>
+        <v>0.5544554455445544</v>
       </c>
       <c r="W9">
-        <v>0.1226927252985885</v>
+        <v>0.1068627450980392</v>
       </c>
       <c r="X9">
-        <v>0.07697577764364623</v>
+        <v>0.1232869513395454</v>
       </c>
       <c r="Y9">
-        <v>0.04571694765494223</v>
-      </c>
-      <c r="Z9">
-        <v>18.89473684210522</v>
-      </c>
-      <c r="AA9">
-        <v>3.056322624743671</v>
+        <v>-0.01642420624150621</v>
       </c>
       <c r="AB9">
-        <v>0.07697577764364623</v>
-      </c>
-      <c r="AC9">
-        <v>2.979346847100025</v>
+        <v>0.122780062569303</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AG9">
-        <v>-8.83</v>
+        <v>-11.017</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.008978069960261003</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.02032655781406198</v>
       </c>
       <c r="AJ9">
-        <v>-0.4630309386470897</v>
+        <v>-1.199716868125885</v>
       </c>
       <c r="AK9">
-        <v>-14.24193548387099</v>
+        <v>5.014565316340466</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>0.1211920529801324</v>
+      </c>
+      <c r="AO9">
+        <v>46</v>
       </c>
       <c r="AP9">
-        <v>-5.351515151515152</v>
+        <v>-7.296026490066224</v>
+      </c>
+      <c r="AQ9">
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -1510,7 +1504,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Provati Insurance Company Limited (DSE:PROVATIINS)</t>
+          <t>Desh General Insurance Company Limited (DSE:DGIC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1519,43 +1513,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.177</v>
+        <v>0.191</v>
+      </c>
+      <c r="E10">
+        <v>0.302</v>
       </c>
       <c r="G10">
-        <v>-0.1388888888888889</v>
+        <v>0.3517915309446255</v>
       </c>
       <c r="H10">
-        <v>-0.1388888888888889</v>
+        <v>0.3517915309446255</v>
       </c>
       <c r="I10">
-        <v>-0.08518518518518518</v>
+        <v>0.3110749185667753</v>
       </c>
       <c r="J10">
-        <v>-0.08518518518518518</v>
+        <v>0.1974269389498738</v>
       </c>
       <c r="K10">
-        <v>-1.31</v>
+        <v>0.541</v>
       </c>
       <c r="L10">
-        <v>-0.1212962962962963</v>
+        <v>0.1762214983713355</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>0.471</v>
       </c>
       <c r="N10">
-        <v>0.02048192771084337</v>
+        <v>0.03738095238095238</v>
       </c>
       <c r="O10">
-        <v>-0.7786259541984732</v>
+        <v>0.8706099815157116</v>
       </c>
       <c r="P10">
-        <v>1.02</v>
+        <v>0.471</v>
       </c>
       <c r="Q10">
-        <v>0.02048192771084337</v>
+        <v>0.03738095238095238</v>
       </c>
       <c r="R10">
-        <v>-0.7786259541984732</v>
+        <v>0.8706099815157116</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1564,31 +1561,16 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>9.02</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>0.1811244979919679</v>
-      </c>
-      <c r="W10">
-        <v>-0.1801925722145805</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>0.07697577764364623</v>
-      </c>
-      <c r="Y10">
-        <v>-0.2571683498582267</v>
-      </c>
-      <c r="Z10">
-        <v>-23.99999999999999</v>
-      </c>
-      <c r="AA10">
-        <v>2.044444444444444</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AB10">
-        <v>0.07697577764364623</v>
-      </c>
-      <c r="AC10">
-        <v>1.967468666800798</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -1600,31 +1582,31 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>-9.02</v>
+        <v>0</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
       <c r="AJ10">
-        <v>-0.2211868563021089</v>
-      </c>
-      <c r="AK10">
-        <v>20.97674418604652</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AN10">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>11.9375</v>
       </c>
       <c r="AP10">
-        <v>12.28882833787466</v>
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>11.9375</v>
       </c>
     </row>
     <row r="11">
@@ -1644,46 +1626,46 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0679</v>
+        <v>0.0677</v>
       </c>
       <c r="E11">
-        <v>0.118</v>
+        <v>0.102</v>
       </c>
       <c r="G11">
-        <v>0.342042755344418</v>
+        <v>0.4711111111111111</v>
       </c>
       <c r="H11">
-        <v>0.342042755344418</v>
+        <v>0.4711111111111111</v>
       </c>
       <c r="I11">
-        <v>0.3871733966745843</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="J11">
-        <v>0.2938670128797155</v>
+        <v>0.221271676300578</v>
       </c>
       <c r="K11">
-        <v>1.22</v>
+        <v>0.989</v>
       </c>
       <c r="L11">
-        <v>0.2897862232779098</v>
+        <v>0.2197777777777778</v>
       </c>
       <c r="M11">
-        <v>0.599</v>
+        <v>0.759</v>
       </c>
       <c r="N11">
-        <v>0.01761764705882353</v>
+        <v>0.0443859649122807</v>
       </c>
       <c r="O11">
-        <v>0.4909836065573771</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="P11">
-        <v>0.599</v>
+        <v>0.759</v>
       </c>
       <c r="Q11">
-        <v>0.01761764705882353</v>
+        <v>0.0443859649122807</v>
       </c>
       <c r="R11">
-        <v>0.4909836065573771</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1692,31 +1674,31 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>10.8</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="V11">
-        <v>0.3176470588235294</v>
+        <v>0.5573099415204678</v>
       </c>
       <c r="W11">
-        <v>0.1184466019417476</v>
+        <v>0.08990909090909091</v>
       </c>
       <c r="X11">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y11">
-        <v>0.04147082429810134</v>
+        <v>-0.03286435449759016</v>
       </c>
       <c r="Z11">
-        <v>2.536144578313253</v>
+        <v>22.50000000000008</v>
       </c>
       <c r="AA11">
-        <v>0.7452892314600014</v>
+        <v>4.978612716763023</v>
       </c>
       <c r="AB11">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC11">
-        <v>0.6683134538163551</v>
+        <v>4.855839271356342</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1728,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>-10.8</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1737,10 +1719,10 @@
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-0.4655172413793104</v>
+        <v>-1.25891677675033</v>
       </c>
       <c r="AK11">
-        <v>-54.0000000000002</v>
+        <v>-953.0000000000202</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1752,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>-6.242774566473989</v>
+        <v>-5.207650273224044</v>
       </c>
     </row>
     <row r="12">
@@ -1772,46 +1754,43 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.299</v>
-      </c>
-      <c r="E12">
-        <v>0.161</v>
+        <v>0.495</v>
       </c>
       <c r="G12">
-        <v>0.2624020887728459</v>
+        <v>0.1995987963891675</v>
       </c>
       <c r="H12">
-        <v>0.2624020887728459</v>
+        <v>0.1995987963891675</v>
       </c>
       <c r="I12">
-        <v>0.2049608355091384</v>
+        <v>0.09287863590772316</v>
       </c>
       <c r="J12">
-        <v>0.1629723310124746</v>
+        <v>0.07098416838605145</v>
       </c>
       <c r="K12">
-        <v>1.15</v>
+        <v>0.616</v>
       </c>
       <c r="L12">
-        <v>0.150130548302872</v>
+        <v>0.06178535606820461</v>
       </c>
       <c r="M12">
-        <v>0.191</v>
+        <v>0.499</v>
       </c>
       <c r="N12">
-        <v>0.007403100775193798</v>
+        <v>0.04056910569105691</v>
       </c>
       <c r="O12">
-        <v>0.1660869565217392</v>
+        <v>0.810064935064935</v>
       </c>
       <c r="P12">
-        <v>0.191</v>
+        <v>0.499</v>
       </c>
       <c r="Q12">
-        <v>0.007403100775193798</v>
+        <v>0.04056910569105691</v>
       </c>
       <c r="R12">
-        <v>0.1660869565217392</v>
+        <v>0.810064935064935</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1820,73 +1799,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>6.73</v>
+        <v>6.85</v>
       </c>
       <c r="V12">
-        <v>0.2608527131782946</v>
+        <v>0.556910569105691</v>
       </c>
       <c r="W12">
-        <v>0.1903973509933775</v>
+        <v>0.09263157894736841</v>
       </c>
       <c r="X12">
-        <v>0.07741772178803703</v>
+        <v>0.1228563947856803</v>
       </c>
       <c r="Y12">
-        <v>0.1129796292053404</v>
+        <v>-0.03022481583831192</v>
       </c>
       <c r="Z12">
-        <v>3.682692307692307</v>
+        <v>51.65803108808301</v>
       </c>
       <c r="AA12">
-        <v>0.6001769497863249</v>
+        <v>3.666902377248365</v>
       </c>
       <c r="AB12">
-        <v>0.07702121777247876</v>
+        <v>0.1227782705935385</v>
       </c>
       <c r="AC12">
-        <v>0.5231557320138461</v>
+        <v>3.544124106654826</v>
       </c>
       <c r="AD12">
-        <v>0.273</v>
+        <v>0.018</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.273</v>
+        <v>0.018</v>
       </c>
       <c r="AG12">
-        <v>-6.457000000000001</v>
+        <v>-6.832</v>
       </c>
       <c r="AH12">
-        <v>0.01047060177194799</v>
+        <v>0.001461276181198246</v>
       </c>
       <c r="AI12">
-        <v>0.03943377148634985</v>
+        <v>0.003328402366863905</v>
       </c>
       <c r="AJ12">
-        <v>-0.333815850695342</v>
+        <v>-1.249451353328456</v>
       </c>
       <c r="AK12">
-        <v>-33.45595854922287</v>
+        <v>4.737864077669903</v>
       </c>
       <c r="AL12">
-        <v>0.065</v>
+        <v>0.017</v>
       </c>
       <c r="AM12">
-        <v>0.065</v>
+        <v>0.017</v>
       </c>
       <c r="AN12">
-        <v>0.1625</v>
+        <v>0.0174757281553398</v>
       </c>
       <c r="AO12">
-        <v>24.15384615384615</v>
+        <v>54.47058823529412</v>
       </c>
       <c r="AP12">
-        <v>-3.843452380952382</v>
+        <v>-6.633009708737863</v>
       </c>
       <c r="AQ12">
-        <v>24.15384615384615</v>
+        <v>54.47058823529412</v>
       </c>
     </row>
     <row r="13">
@@ -1897,7 +1876,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prime Insurance Company Limited (DSE:PRIMEINSUR)</t>
+          <t>Express Insurance Limited (DSE:EIL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1905,47 +1884,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.0372</v>
-      </c>
-      <c r="E13">
-        <v>0.0144</v>
-      </c>
       <c r="G13">
-        <v>0.2881720430107527</v>
+        <v>0.8798076923076923</v>
       </c>
       <c r="H13">
-        <v>0.2881720430107527</v>
+        <v>0.8798076923076923</v>
       </c>
       <c r="I13">
-        <v>0.2838709677419355</v>
+        <v>0.764423076923077</v>
       </c>
       <c r="J13">
-        <v>0.2149023171285779</v>
+        <v>0.5525949953660797</v>
       </c>
       <c r="K13">
-        <v>1.08</v>
+        <v>0.66</v>
       </c>
       <c r="L13">
-        <v>0.232258064516129</v>
+        <v>0.3173076923076923</v>
       </c>
       <c r="M13">
-        <v>0.506</v>
+        <v>0.134</v>
       </c>
       <c r="N13">
-        <v>0.01297435897435897</v>
+        <v>0.007745664739884394</v>
       </c>
       <c r="O13">
-        <v>0.4685185185185185</v>
+        <v>0.203030303030303</v>
       </c>
       <c r="P13">
-        <v>0.506</v>
+        <v>0.134</v>
       </c>
       <c r="Q13">
-        <v>0.01297435897435897</v>
+        <v>0.007745664739884394</v>
       </c>
       <c r="R13">
-        <v>0.4685185185185185</v>
+        <v>0.203030303030303</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1954,31 +1927,31 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>6.06</v>
+        <v>12.7</v>
       </c>
       <c r="V13">
-        <v>0.1553846153846154</v>
+        <v>0.7341040462427745</v>
       </c>
       <c r="W13">
-        <v>0.1287246722288439</v>
+        <v>0.05238095238095238</v>
       </c>
       <c r="X13">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y13">
-        <v>0.05174889458519764</v>
+        <v>-0.0703924930257287</v>
       </c>
       <c r="Z13">
-        <v>2.527173913043478</v>
+        <v>2.31111111111111</v>
       </c>
       <c r="AA13">
-        <v>0.5430955296999386</v>
+        <v>1.277108433734939</v>
       </c>
       <c r="AB13">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC13">
-        <v>0.4661197520562924</v>
+        <v>1.154334988328258</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -1990,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-6.06</v>
+        <v>-12.7</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -1999,22 +1972,28 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.1839708561020036</v>
+        <v>-2.76086956521739</v>
       </c>
       <c r="AK13">
-        <v>-2.075342465753424</v>
+        <v>127.0000000000004</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>79.5</v>
+      </c>
       <c r="AP13">
-        <v>-4.150684931506849</v>
+        <v>-7.341040462427745</v>
+      </c>
+      <c r="AQ13">
+        <v>79.5</v>
       </c>
     </row>
     <row r="14">
@@ -2025,7 +2004,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paramount Insurance Company Limited (DSE:PARAMOUNT)</t>
+          <t>Takaful Islami Insurance Limited (DSE:TAKAFULINS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2034,76 +2013,79 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.234</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E14">
-        <v>0.401</v>
+        <v>0.0133</v>
       </c>
       <c r="G14">
-        <v>0.6171548117154811</v>
+        <v>0.3036750483558994</v>
       </c>
       <c r="H14">
-        <v>0.6171548117154811</v>
+        <v>0.3036750483558994</v>
       </c>
       <c r="I14">
-        <v>0.5983263598326359</v>
+        <v>0.1895551257253385</v>
       </c>
       <c r="J14">
-        <v>0.4654349262277032</v>
+        <v>0.1453189242625087</v>
       </c>
       <c r="K14">
-        <v>2.22</v>
+        <v>0.726</v>
       </c>
       <c r="L14">
-        <v>0.4644351464435146</v>
+        <v>0.1404255319148936</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>0.465</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.02473404255319149</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0.6404958677685951</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>0.465</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.02473404255319149</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.6404958677685951</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>6.04</v>
+        <v>6.7</v>
       </c>
       <c r="V14">
-        <v>0.1730659025787966</v>
+        <v>0.3563829787234042</v>
       </c>
       <c r="W14">
-        <v>0.222</v>
+        <v>0.07682539682539682</v>
       </c>
       <c r="X14">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y14">
-        <v>0.1450242223563538</v>
+        <v>-0.04594804858128425</v>
       </c>
       <c r="Z14">
-        <v>1.096330275229358</v>
+        <v>8.338709677419365</v>
       </c>
       <c r="AA14">
-        <v>0.5102704007725737</v>
+        <v>1.211772320059953</v>
       </c>
       <c r="AB14">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC14">
-        <v>0.4332946231289275</v>
+        <v>1.088998874653272</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2115,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>-6.04</v>
+        <v>-6.7</v>
       </c>
       <c r="AH14">
         <v>0</v>
@@ -2124,10 +2106,10 @@
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>-0.2092862092862093</v>
+        <v>-0.5537190082644627</v>
       </c>
       <c r="AK14">
-        <v>-0.9805194805194807</v>
+        <v>-5.583333333333333</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2139,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>-2.075601374570446</v>
+        <v>-6.38095238095238</v>
       </c>
     </row>
     <row r="15">
@@ -2150,7 +2132,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Karnaphuli Insurance Company Limited (DSE:KARNAPHULI)</t>
+          <t>Karnaphuli Insurance Co. Ltd. (DSE:KARNAPHULI)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2159,46 +2141,46 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.118</v>
+        <v>0.138</v>
       </c>
       <c r="E15">
-        <v>0.3720000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="G15">
-        <v>0.259825327510917</v>
+        <v>0.3723849372384937</v>
       </c>
       <c r="H15">
-        <v>0.259825327510917</v>
+        <v>0.3723849372384937</v>
       </c>
       <c r="I15">
-        <v>0.3100436681222707</v>
+        <v>0.2970711297071129</v>
       </c>
       <c r="J15">
-        <v>0.2297841370126049</v>
+        <v>0.2186192468619247</v>
       </c>
       <c r="K15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="L15">
-        <v>0.2292576419213974</v>
+        <v>0.2175732217573222</v>
       </c>
       <c r="M15">
-        <v>0.529</v>
+        <v>0.535</v>
       </c>
       <c r="N15">
-        <v>0.02361607142857143</v>
+        <v>0.04458333333333334</v>
       </c>
       <c r="O15">
-        <v>0.5038095238095238</v>
+        <v>0.514423076923077</v>
       </c>
       <c r="P15">
-        <v>0.529</v>
+        <v>0.535</v>
       </c>
       <c r="Q15">
-        <v>0.02361607142857143</v>
+        <v>0.04458333333333334</v>
       </c>
       <c r="R15">
-        <v>0.5038095238095238</v>
+        <v>0.514423076923077</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2207,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>8.699999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="V15">
-        <v>0.3883928571428572</v>
+        <v>0.665</v>
       </c>
       <c r="W15">
-        <v>0.1054216867469879</v>
+        <v>0.1009708737864078</v>
       </c>
       <c r="X15">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y15">
-        <v>0.02844590910334172</v>
+        <v>-0.02180257162027331</v>
       </c>
       <c r="Z15">
-        <v>2.00877192982456</v>
+        <v>3.229729729729729</v>
       </c>
       <c r="AA15">
-        <v>0.4615839243498815</v>
+        <v>0.7060810810810808</v>
       </c>
       <c r="AB15">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC15">
-        <v>0.3846081467062353</v>
+        <v>0.5833076356743997</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2243,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>-8.699999999999999</v>
+        <v>-7.98</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -2252,28 +2234,28 @@
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>-0.635036496350365</v>
+        <v>-1.985074626865672</v>
       </c>
       <c r="AK15">
-        <v>-4.833333333333331</v>
+        <v>-6.650000000000004</v>
       </c>
       <c r="AL15">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AM15">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AN15">
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>284</v>
+        <v>710</v>
       </c>
       <c r="AP15">
-        <v>-5.878378378378378</v>
+        <v>-5.32</v>
       </c>
       <c r="AQ15">
-        <v>284</v>
+        <v>710</v>
       </c>
     </row>
     <row r="16">
@@ -2284,7 +2266,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Janata Insurance Company Limited (DSE:JANATAINS)</t>
+          <t>Prime Insurance Company Limited (DSE:PRIMEINSUR)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2293,46 +2275,46 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0833</v>
+        <v>0.177</v>
       </c>
       <c r="E16">
-        <v>0.263</v>
+        <v>0.0633</v>
       </c>
       <c r="G16">
-        <v>0.2994350282485876</v>
+        <v>0.1507479861910242</v>
       </c>
       <c r="H16">
-        <v>0.2994350282485876</v>
+        <v>0.1507479861910242</v>
       </c>
       <c r="I16">
-        <v>0.2966101694915254</v>
+        <v>0.1760644418872267</v>
       </c>
       <c r="J16">
-        <v>0.2119074686509577</v>
+        <v>0.1279090680465481</v>
       </c>
       <c r="K16">
-        <v>0.703</v>
+        <v>1.1</v>
       </c>
       <c r="L16">
-        <v>0.1985875706214689</v>
+        <v>0.1265822784810127</v>
       </c>
       <c r="M16">
-        <v>0.62</v>
+        <v>0.575</v>
       </c>
       <c r="N16">
-        <v>0.025</v>
+        <v>0.01747720364741641</v>
       </c>
       <c r="O16">
-        <v>0.8819345661450925</v>
+        <v>0.5227272727272726</v>
       </c>
       <c r="P16">
-        <v>0.62</v>
+        <v>0.575</v>
       </c>
       <c r="Q16">
-        <v>0.025</v>
+        <v>0.01747720364741641</v>
       </c>
       <c r="R16">
-        <v>0.8819345661450925</v>
+        <v>0.5227272727272726</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2341,31 +2323,31 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>5.59</v>
+        <v>6.18</v>
       </c>
       <c r="V16">
-        <v>0.2254032258064516</v>
+        <v>0.1878419452887538</v>
       </c>
       <c r="W16">
-        <v>0.09201570680628272</v>
+        <v>0.1224944320712695</v>
       </c>
       <c r="X16">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y16">
-        <v>0.0150399291626365</v>
+        <v>-0.000279013335411582</v>
       </c>
       <c r="Z16">
-        <v>1.51931330472103</v>
+        <v>2.976027397260273</v>
       </c>
       <c r="AA16">
-        <v>0.3219538364911546</v>
+        <v>0.3806608908645558</v>
       </c>
       <c r="AB16">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC16">
-        <v>0.2449780588475084</v>
+        <v>0.2578874454578748</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2377,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>-5.59</v>
+        <v>-6.18</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2386,28 +2368,22 @@
         <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.290994273815721</v>
+        <v>-0.2312874251497006</v>
       </c>
       <c r="AK16">
-        <v>-2.866666666666666</v>
+        <v>-3.304812834224597</v>
       </c>
       <c r="AL16">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="AN16">
         <v>0</v>
       </c>
-      <c r="AO16">
-        <v>25.60975609756098</v>
-      </c>
       <c r="AP16">
-        <v>-4.946902654867257</v>
-      </c>
-      <c r="AQ16">
-        <v>25.60975609756098</v>
+        <v>-3.395604395604396</v>
       </c>
     </row>
     <row r="17">
@@ -2418,7 +2394,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crystal Insurance Company Limited (DSE:CRYSTALINS)</t>
+          <t>Janata Insurance Company Limited (DSE:JANATAINS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2426,41 +2402,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D17">
+        <v>0.0771</v>
+      </c>
+      <c r="E17">
+        <v>0.235</v>
+      </c>
       <c r="G17">
-        <v>0.8951612903225807</v>
+        <v>0.2952127659574468</v>
       </c>
       <c r="H17">
-        <v>0.8951612903225807</v>
+        <v>0.2952127659574468</v>
       </c>
       <c r="I17">
-        <v>0.7620967741935484</v>
+        <v>0.2372340425531915</v>
       </c>
       <c r="J17">
-        <v>0.7620967741935484</v>
+        <v>0.1523262580008602</v>
       </c>
       <c r="K17">
-        <v>1.84</v>
+        <v>0.54</v>
       </c>
       <c r="L17">
-        <v>0.7419354838709677</v>
+        <v>0.1436170212765958</v>
       </c>
       <c r="M17">
-        <v>0.428</v>
+        <v>0.323</v>
       </c>
       <c r="N17">
-        <v>0.01615094339622641</v>
+        <v>0.02484615384615385</v>
       </c>
       <c r="O17">
-        <v>0.2326086956521739</v>
+        <v>0.5981481481481481</v>
       </c>
       <c r="P17">
-        <v>0.428</v>
+        <v>0.323</v>
       </c>
       <c r="Q17">
-        <v>0.01615094339622641</v>
+        <v>0.02484615384615385</v>
       </c>
       <c r="R17">
-        <v>0.2326086956521739</v>
+        <v>0.5981481481481481</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2469,73 +2451,73 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.437</v>
+        <v>5.24</v>
       </c>
       <c r="V17">
-        <v>0.01649056603773585</v>
+        <v>0.4030769230769231</v>
       </c>
       <c r="W17">
-        <v>0.2746268656716418</v>
+        <v>0.07161803713527852</v>
       </c>
       <c r="X17">
-        <v>0.07707664683588041</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y17">
-        <v>0.1975502188357614</v>
+        <v>-0.05115540827140255</v>
       </c>
       <c r="Z17">
-        <v>0.4074256612452768</v>
+        <v>1.928205128205128</v>
       </c>
       <c r="AA17">
-        <v>0.3104977821586989</v>
+        <v>0.2937162718375559</v>
       </c>
       <c r="AB17">
-        <v>0.0769911881408238</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC17">
-        <v>0.2335065940178751</v>
+        <v>0.1709428264308749</v>
       </c>
       <c r="AD17">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>-0.373</v>
+        <v>-5.24</v>
       </c>
       <c r="AH17">
-        <v>0.002409275711489234</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>0.006449012494961709</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>-0.0142764190301221</v>
+        <v>-0.6752577319587629</v>
       </c>
       <c r="AK17">
-        <v>-0.03931696005059555</v>
+        <v>-3.881481481481483</v>
       </c>
       <c r="AL17">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="AM17">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="AN17">
-        <v>0.02770562770562771</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>171.8181818181818</v>
+        <v>28.7741935483871</v>
       </c>
       <c r="AP17">
-        <v>-0.1614718614718615</v>
+        <v>-5.521601685985248</v>
       </c>
       <c r="AQ17">
-        <v>171.8181818181818</v>
+        <v>28.7741935483871</v>
       </c>
     </row>
     <row r="18">
@@ -2546,7 +2528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>City General Insurance Company Limited (DSE:CITYGENINS)</t>
+          <t>Eastern Insurance Company Limited (DSE:EASTERNINS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2554,47 +2536,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.104</v>
-      </c>
-      <c r="E18">
-        <v>0.173</v>
-      </c>
       <c r="G18">
-        <v>0.2871428571428571</v>
+        <v>0.7888631090487239</v>
       </c>
       <c r="H18">
-        <v>0.2871428571428571</v>
+        <v>0.7888631090487239</v>
       </c>
       <c r="I18">
-        <v>0.3457142857142857</v>
+        <v>0.4895591647331787</v>
       </c>
       <c r="J18">
-        <v>0.26716915720263</v>
+        <v>0.4047647065353746</v>
       </c>
       <c r="K18">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="L18">
-        <v>0.2642857142857143</v>
+        <v>0.4013921113689096</v>
       </c>
       <c r="M18">
-        <v>0.803</v>
+        <v>0.79</v>
       </c>
       <c r="N18">
-        <v>0.02341107871720117</v>
+        <v>0.0383495145631068</v>
       </c>
       <c r="O18">
-        <v>0.4340540540540541</v>
+        <v>0.4566473988439307</v>
       </c>
       <c r="P18">
-        <v>0.803</v>
+        <v>0.79</v>
       </c>
       <c r="Q18">
-        <v>0.02341107871720117</v>
+        <v>0.0383495145631068</v>
       </c>
       <c r="R18">
-        <v>0.4340540540540541</v>
+        <v>0.4566473988439307</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2603,31 +2579,31 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>7.89</v>
+        <v>14.9</v>
       </c>
       <c r="V18">
-        <v>0.2300291545189505</v>
+        <v>0.7233009708737864</v>
       </c>
       <c r="W18">
-        <v>0.137037037037037</v>
+        <v>0.07972350230414747</v>
       </c>
       <c r="X18">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y18">
-        <v>0.06006125939339081</v>
+        <v>-0.0430499431025336</v>
       </c>
       <c r="Z18">
-        <v>1.020408163265306</v>
+        <v>0.6951612903225807</v>
       </c>
       <c r="AA18">
-        <v>0.2726215889822755</v>
+        <v>0.2813767556721716</v>
       </c>
       <c r="AB18">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC18">
-        <v>0.1956458113386293</v>
+        <v>0.1586033102654906</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -2639,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>-7.89</v>
+        <v>-14.9</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -2648,28 +2624,28 @@
         <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-0.2987504733055661</v>
+        <v>-2.614035087719298</v>
       </c>
       <c r="AK18">
-        <v>-1.158590308370044</v>
+        <v>-2.403225806451613</v>
       </c>
       <c r="AL18">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="AM18">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="AN18">
         <v>0</v>
       </c>
       <c r="AO18">
-        <v>484</v>
+        <v>263.75</v>
       </c>
       <c r="AP18">
-        <v>-3.181451612903226</v>
+        <v>-6.898148148148148</v>
       </c>
       <c r="AQ18">
-        <v>484</v>
+        <v>263.75</v>
       </c>
     </row>
     <row r="19">
@@ -2680,7 +2656,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Republic Insurance Company Limited (DSE:REPUBLIC)</t>
+          <t>Pioneer Insurance Company Limited (DSE:PIONEERINS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2689,46 +2665,46 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.105</v>
+        <v>0.0367</v>
       </c>
       <c r="E19">
-        <v>0.219</v>
+        <v>0.253</v>
       </c>
       <c r="G19">
-        <v>0.3221757322175732</v>
+        <v>0.523076923076923</v>
       </c>
       <c r="H19">
-        <v>0.3221757322175732</v>
+        <v>0.523076923076923</v>
       </c>
       <c r="I19">
-        <v>0.3626220362622036</v>
+        <v>0.4353846153846154</v>
       </c>
       <c r="J19">
-        <v>0.2707208789804849</v>
+        <v>0.3064776365133083</v>
       </c>
       <c r="K19">
-        <v>1.95</v>
+        <v>5.93</v>
       </c>
       <c r="L19">
-        <v>0.2719665271966527</v>
+        <v>0.3041025641025641</v>
       </c>
       <c r="M19">
-        <v>0.542</v>
+        <v>1.5</v>
       </c>
       <c r="N19">
-        <v>0.0175974025974026</v>
+        <v>0.02546689303904924</v>
       </c>
       <c r="O19">
-        <v>0.2779487179487179</v>
+        <v>0.2529510961214165</v>
       </c>
       <c r="P19">
-        <v>0.542</v>
+        <v>1.5</v>
       </c>
       <c r="Q19">
-        <v>0.0175974025974026</v>
+        <v>0.02546689303904924</v>
       </c>
       <c r="R19">
-        <v>0.2779487179487179</v>
+        <v>0.2529510961214165</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2737,55 +2713,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.893</v>
+        <v>22.6</v>
       </c>
       <c r="V19">
-        <v>0.02899350649350649</v>
+        <v>0.3837011884550085</v>
       </c>
       <c r="W19">
-        <v>0.2326968973747016</v>
+        <v>0.1323660714285714</v>
       </c>
       <c r="X19">
-        <v>0.07711002598264093</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y19">
-        <v>0.1555868713920607</v>
+        <v>0.009592626021890358</v>
       </c>
       <c r="Z19">
-        <v>0.9585561497326202</v>
+        <v>0.8024691358024693</v>
       </c>
       <c r="AA19">
-        <v>0.2595011634077642</v>
+        <v>0.2459388441156178</v>
       </c>
       <c r="AB19">
-        <v>0.07698968224947425</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC19">
-        <v>0.1825114811582899</v>
+        <v>0.1231653987089368</v>
       </c>
       <c r="AD19">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>-0.794</v>
+        <v>-22.6</v>
       </c>
       <c r="AH19">
-        <v>0.003203987184051264</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>0.01026013058348015</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>-0.02646137439178831</v>
+        <v>-0.6225895316804408</v>
       </c>
       <c r="AK19">
-        <v>-0.09068067610781179</v>
+        <v>-1.076190476190476</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2794,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="AN19">
-        <v>0.03666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>-0.294074074074074</v>
+        <v>-2.603686635944701</v>
       </c>
     </row>
     <row r="20">
@@ -2808,7 +2784,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Continental Insurance Limited (DSE:CONTININS)</t>
+          <t>Central Insurance Company Limited (DSE:CENTRALINS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2817,46 +2793,46 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0323</v>
+        <v>0.0766</v>
       </c>
       <c r="E20">
-        <v>0.0434</v>
+        <v>0.142</v>
       </c>
       <c r="G20">
-        <v>0.2678983833718245</v>
+        <v>0.5458422174840085</v>
       </c>
       <c r="H20">
-        <v>0.2678983833718245</v>
+        <v>0.5458422174840085</v>
       </c>
       <c r="I20">
-        <v>0.3210161662817552</v>
+        <v>0.4093816631130063</v>
       </c>
       <c r="J20">
-        <v>0.2197343215711549</v>
+        <v>0.3454157782515991</v>
       </c>
       <c r="K20">
-        <v>0.882</v>
+        <v>1.62</v>
       </c>
       <c r="L20">
-        <v>0.2036951501154734</v>
+        <v>0.3454157782515991</v>
       </c>
       <c r="M20">
-        <v>0.299</v>
+        <v>0.912</v>
       </c>
       <c r="N20">
-        <v>0.01294372294372294</v>
+        <v>0.0492972972972973</v>
       </c>
       <c r="O20">
-        <v>0.3390022675736961</v>
+        <v>0.562962962962963</v>
       </c>
       <c r="P20">
-        <v>0.299</v>
+        <v>0.912</v>
       </c>
       <c r="Q20">
-        <v>0.01294372294372294</v>
+        <v>0.0492972972972973</v>
       </c>
       <c r="R20">
-        <v>0.3390022675736961</v>
+        <v>0.562962962962963</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2865,31 +2841,31 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>5.52</v>
+        <v>7.67</v>
       </c>
       <c r="V20">
-        <v>0.2389610389610389</v>
+        <v>0.4145945945945946</v>
       </c>
       <c r="W20">
-        <v>0.09494079655543596</v>
+        <v>0.1045161290322581</v>
       </c>
       <c r="X20">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y20">
-        <v>0.01796501891178973</v>
+        <v>-0.018257316374423</v>
       </c>
       <c r="Z20">
-        <v>1.113110539845759</v>
+        <v>0.6937869822485208</v>
       </c>
       <c r="AA20">
-        <v>0.2445885893067098</v>
+        <v>0.2396449704142012</v>
       </c>
       <c r="AB20">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC20">
-        <v>0.1676128116630636</v>
+        <v>0.1168715250075201</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -2901,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>-5.52</v>
+        <v>-7.67</v>
       </c>
       <c r="AH20">
         <v>0</v>
@@ -2910,28 +2886,22 @@
         <v>0</v>
       </c>
       <c r="AJ20">
-        <v>-0.3139931740614334</v>
+        <v>-0.7082179132040628</v>
       </c>
       <c r="AK20">
-        <v>-1.205240174672489</v>
+        <v>-0.4161692892023874</v>
       </c>
       <c r="AL20">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN20">
         <v>0</v>
       </c>
-      <c r="AO20">
-        <v>16.16279069767442</v>
-      </c>
       <c r="AP20">
-        <v>-3.729729729729729</v>
-      </c>
-      <c r="AQ20">
-        <v>16.16279069767442</v>
+        <v>-3.567441860465117</v>
       </c>
     </row>
     <row r="21">
@@ -2942,7 +2912,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Central Insurance Company Limited (DSE:CENTRALINS)</t>
+          <t>Northern Islami Insurance Limited (DSE:NORTHRNINS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2951,46 +2921,46 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.0489</v>
+        <v>0.259</v>
       </c>
       <c r="E21">
-        <v>0.136</v>
+        <v>0.0352</v>
       </c>
       <c r="G21">
-        <v>0.3885480572597137</v>
+        <v>0.1321160042964554</v>
       </c>
       <c r="H21">
-        <v>0.3885480572597137</v>
+        <v>0.1321160042964554</v>
       </c>
       <c r="I21">
-        <v>0.4314928425357873</v>
+        <v>0.112781954887218</v>
       </c>
       <c r="J21">
-        <v>0.3279760500235961</v>
+        <v>0.08371891266628109</v>
       </c>
       <c r="K21">
-        <v>1.58</v>
+        <v>0.772</v>
       </c>
       <c r="L21">
-        <v>0.3231083844580778</v>
+        <v>0.08292158968850698</v>
       </c>
       <c r="M21">
-        <v>0.552</v>
+        <v>0.442</v>
       </c>
       <c r="N21">
-        <v>0.01595375722543352</v>
+        <v>0.02695121951219513</v>
       </c>
       <c r="O21">
-        <v>0.349367088607595</v>
+        <v>0.572538860103627</v>
       </c>
       <c r="P21">
-        <v>0.552</v>
+        <v>0.442</v>
       </c>
       <c r="Q21">
-        <v>0.01595375722543352</v>
+        <v>0.02695121951219513</v>
       </c>
       <c r="R21">
-        <v>0.349367088607595</v>
+        <v>0.572538860103627</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2999,31 +2969,31 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>8.74</v>
+        <v>7.65</v>
       </c>
       <c r="V21">
-        <v>0.2526011560693642</v>
+        <v>0.4664634146341464</v>
       </c>
       <c r="W21">
-        <v>0.1104895104895105</v>
+        <v>0.07423076923076923</v>
       </c>
       <c r="X21">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y21">
-        <v>0.03351373284586426</v>
+        <v>-0.04854267617591185</v>
       </c>
       <c r="Z21">
-        <v>0.7364457831325301</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="AA21">
-        <v>0.2415365790083411</v>
+        <v>0.2272370486656201</v>
       </c>
       <c r="AB21">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC21">
-        <v>0.1645608013646948</v>
+        <v>0.104463603258939</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -3035,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>-8.74</v>
+        <v>-7.65</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -3044,28 +3014,22 @@
         <v>0</v>
       </c>
       <c r="AJ21">
-        <v>-0.3379737045630317</v>
+        <v>-0.8742857142857146</v>
       </c>
       <c r="AK21">
-        <v>-1.292899408284024</v>
+        <v>-5.239726027397264</v>
       </c>
       <c r="AL21">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AN21">
         <v>0</v>
       </c>
-      <c r="AO21">
-        <v>87.91666666666666</v>
-      </c>
       <c r="AP21">
-        <v>-3.867256637168142</v>
-      </c>
-      <c r="AQ21">
-        <v>87.91666666666666</v>
+        <v>-6.428571428571429</v>
       </c>
     </row>
     <row r="22">
@@ -3076,7 +3040,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rupali Insurance Company Limited (DSE:RUPALIINS)</t>
+          <t>City General Insurance Company Limited (DSE:CITYGENINS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3085,46 +3049,46 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.0873</v>
+        <v>0.145</v>
       </c>
       <c r="E22">
-        <v>0.0357</v>
+        <v>0.0315</v>
       </c>
       <c r="G22">
-        <v>0.4723926380368099</v>
+        <v>0.2509270704573547</v>
       </c>
       <c r="H22">
-        <v>0.4723926380368099</v>
+        <v>0.2509270704573547</v>
       </c>
       <c r="I22">
-        <v>0.5276073619631902</v>
+        <v>0.242274412855377</v>
       </c>
       <c r="J22">
-        <v>0.3620330191031972</v>
+        <v>0.1716005815405701</v>
       </c>
       <c r="K22">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="L22">
-        <v>0.3456032719836401</v>
+        <v>0.169344870210136</v>
       </c>
       <c r="M22">
-        <v>1.81</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="N22">
-        <v>0.04502487562189054</v>
+        <v>0.03965116279069768</v>
       </c>
       <c r="O22">
-        <v>1.071005917159763</v>
+        <v>0.4978102189781022</v>
       </c>
       <c r="P22">
-        <v>1.81</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="Q22">
-        <v>0.04502487562189054</v>
+        <v>0.03965116279069768</v>
       </c>
       <c r="R22">
-        <v>1.071005917159763</v>
+        <v>0.4978102189781022</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3133,31 +3097,31 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>12</v>
+        <v>7.64</v>
       </c>
       <c r="V22">
-        <v>0.2985074626865671</v>
+        <v>0.4441860465116279</v>
       </c>
       <c r="W22">
-        <v>0.0786046511627907</v>
+        <v>0.09319727891156464</v>
       </c>
       <c r="X22">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y22">
-        <v>0.001628873519144466</v>
+        <v>-0.02957616649511643</v>
       </c>
       <c r="Z22">
-        <v>0.5821428571428571</v>
+        <v>1.187958883994126</v>
       </c>
       <c r="AA22">
-        <v>0.2107549361207898</v>
+        <v>0.2038544353396788</v>
       </c>
       <c r="AB22">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC22">
-        <v>0.1337791584771436</v>
+        <v>0.08108098993299771</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -3169,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>-12</v>
+        <v>-7.64</v>
       </c>
       <c r="AH22">
         <v>0</v>
@@ -3178,22 +3142,28 @@
         <v>0</v>
       </c>
       <c r="AJ22">
-        <v>-0.425531914893617</v>
+        <v>-0.799163179916318</v>
       </c>
       <c r="AK22">
-        <v>-1.2</v>
+        <v>-1.425373134328358</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AN22">
         <v>0</v>
       </c>
+      <c r="AO22">
+        <v>163.3333333333333</v>
+      </c>
       <c r="AP22">
-        <v>-4.761904761904762</v>
+        <v>-3.745098039215686</v>
+      </c>
+      <c r="AQ22">
+        <v>163.3333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -3204,7 +3174,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Asia Insurance Limited (DSE:ASIAINS)</t>
+          <t>Federal Insurance Company Limited (DSE:FEDERALINS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3213,46 +3183,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.08220000000000001</v>
+        <v>0.144</v>
       </c>
       <c r="E23">
-        <v>0.181</v>
+        <v>0.303</v>
       </c>
       <c r="G23">
-        <v>0.3196022727272727</v>
+        <v>0.3248175182481752</v>
       </c>
       <c r="H23">
-        <v>0.3196022727272727</v>
+        <v>0.3248175182481752</v>
       </c>
       <c r="I23">
-        <v>0.3607954545454545</v>
+        <v>0.2937956204379562</v>
       </c>
       <c r="J23">
-        <v>0.2515465909090909</v>
+        <v>0.2095980950685419</v>
       </c>
       <c r="K23">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="L23">
-        <v>0.2485795454545454</v>
+        <v>0.2135036496350365</v>
       </c>
       <c r="M23">
-        <v>1.37</v>
+        <v>0.369</v>
       </c>
       <c r="N23">
-        <v>0.0215748031496063</v>
+        <v>0.02157894736842105</v>
       </c>
       <c r="O23">
-        <v>0.7828571428571429</v>
+        <v>0.3153846153846154</v>
       </c>
       <c r="P23">
-        <v>1.37</v>
+        <v>0.369</v>
       </c>
       <c r="Q23">
-        <v>0.0215748031496063</v>
+        <v>0.02157894736842105</v>
       </c>
       <c r="R23">
-        <v>0.7828571428571429</v>
+        <v>0.3153846153846154</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3261,73 +3231,73 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>0.756</v>
+        <v>5.02</v>
       </c>
       <c r="V23">
-        <v>0.01190551181102362</v>
+        <v>0.2935672514619883</v>
       </c>
       <c r="W23">
-        <v>0.1495726495726496</v>
+        <v>0.1158415841584158</v>
       </c>
       <c r="X23">
-        <v>0.07708759253316762</v>
+        <v>0.1231181784983506</v>
       </c>
       <c r="Y23">
-        <v>0.07248505703948195</v>
+        <v>-0.007276594339934772</v>
       </c>
       <c r="Z23">
-        <v>0.760177086707699</v>
+        <v>0.9617409617409618</v>
       </c>
       <c r="AA23">
-        <v>0.1912199546485261</v>
+        <v>0.201579073530293</v>
       </c>
       <c r="AB23">
-        <v>0.07698736493649486</v>
+        <v>0.1227934065648674</v>
       </c>
       <c r="AC23">
-        <v>0.1142325897120313</v>
+        <v>0.07878566696542563</v>
       </c>
       <c r="AD23">
-        <v>0.17</v>
+        <v>0.104</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0.17</v>
+        <v>0.104</v>
       </c>
       <c r="AG23">
-        <v>-0.586</v>
+        <v>-4.915999999999999</v>
       </c>
       <c r="AH23">
-        <v>0.002670017276582378</v>
+        <v>0.006045105789351313</v>
       </c>
       <c r="AI23">
-        <v>0.01341752170481452</v>
+        <v>0.01126272471301711</v>
       </c>
       <c r="AJ23">
-        <v>-0.0093143020631338</v>
+        <v>-0.4034799737360472</v>
       </c>
       <c r="AK23">
-        <v>-0.04918583179452744</v>
+        <v>-1.166587565258661</v>
       </c>
       <c r="AL23">
-        <v>0.03</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM23">
-        <v>0.03</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN23">
-        <v>0.05923344947735192</v>
+        <v>0.0608187134502924</v>
       </c>
       <c r="AO23">
-        <v>84.66666666666667</v>
+        <v>178.8888888888889</v>
       </c>
       <c r="AP23">
-        <v>-0.2041811846689895</v>
+        <v>-2.874853801169591</v>
       </c>
       <c r="AQ23">
-        <v>84.66666666666667</v>
+        <v>178.8888888888889</v>
       </c>
     </row>
     <row r="24">
@@ -3338,7 +3308,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Green Delta Insurance Company Limited (DSE:GREENDELT)</t>
+          <t>Asia Insurance Limited (DSE:ASIAINS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3347,46 +3317,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.0487</v>
+        <v>0.0823</v>
       </c>
       <c r="E24">
-        <v>0.394</v>
+        <v>0.161</v>
       </c>
       <c r="G24">
-        <v>0.3930817610062893</v>
+        <v>0.4494219653179191</v>
       </c>
       <c r="H24">
-        <v>0.3930817610062893</v>
+        <v>0.4494219653179191</v>
       </c>
       <c r="I24">
-        <v>0.5377358490566038</v>
+        <v>0.3294797687861272</v>
       </c>
       <c r="J24">
-        <v>0.3229755068557366</v>
+        <v>0.2779531970156095</v>
       </c>
       <c r="K24">
-        <v>9.69</v>
+        <v>1.91</v>
       </c>
       <c r="L24">
-        <v>0.3047169811320755</v>
+        <v>0.2760115606936416</v>
       </c>
       <c r="M24">
-        <v>3.05</v>
+        <v>0.719</v>
       </c>
       <c r="N24">
-        <v>0.02447833065810594</v>
+        <v>0.03209821428571429</v>
       </c>
       <c r="O24">
-        <v>0.3147574819401445</v>
+        <v>0.3764397905759163</v>
       </c>
       <c r="P24">
-        <v>3.05</v>
+        <v>0.719</v>
       </c>
       <c r="Q24">
-        <v>0.02447833065810594</v>
+        <v>0.03209821428571429</v>
       </c>
       <c r="R24">
-        <v>0.3147574819401445</v>
+        <v>0.3764397905759163</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3395,67 +3365,73 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>18.3</v>
+        <v>1.7</v>
       </c>
       <c r="V24">
-        <v>0.1468699839486357</v>
+        <v>0.07589285714285715</v>
       </c>
       <c r="W24">
-        <v>0.1290279627163782</v>
+        <v>0.1552845528455284</v>
       </c>
       <c r="X24">
-        <v>0.07697577764364623</v>
+        <v>0.1230998734316269</v>
       </c>
       <c r="Y24">
-        <v>0.05205218507273195</v>
+        <v>0.03218467941390153</v>
       </c>
       <c r="Z24">
-        <v>0.5408163265306123</v>
+        <v>0.671909894164482</v>
       </c>
       <c r="AA24">
-        <v>0.174670427177082</v>
+        <v>0.1867595031894376</v>
       </c>
       <c r="AB24">
-        <v>0.07697577764364623</v>
+        <v>0.1227776656415158</v>
       </c>
       <c r="AC24">
-        <v>0.0976946495334358</v>
+        <v>0.0639818375479218</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AG24">
-        <v>-18.3</v>
+        <v>-1.571</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>0.00572595321585512</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>0.01128707673462245</v>
       </c>
       <c r="AJ24">
-        <v>-0.1721542803386642</v>
+        <v>-0.07542368812713045</v>
       </c>
       <c r="AK24">
-        <v>-0.2909379968203498</v>
+        <v>-0.161475999588858</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>0.05139442231075698</v>
+      </c>
+      <c r="AO24">
+        <v>87.69230769230769</v>
       </c>
       <c r="AP24">
-        <v>-1.033898305084746</v>
+        <v>-0.6258964143426295</v>
+      </c>
+      <c r="AQ24">
+        <v>87.69230769230769</v>
       </c>
     </row>
     <row r="25">
@@ -3466,7 +3442,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dhaka Insurance Limited (DSE:DHAKAINS)</t>
+          <t>Continental Insurance Limited (DSE:CONTININS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3475,46 +3451,46 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.0883</v>
+        <v>0.04</v>
       </c>
       <c r="E25">
-        <v>0.01</v>
+        <v>0.0253</v>
       </c>
       <c r="G25">
-        <v>0.2647702407002188</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H25">
-        <v>0.2647702407002188</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I25">
-        <v>0.3107221006564551</v>
+        <v>0.2214285714285714</v>
       </c>
       <c r="J25">
-        <v>0.1553610503282276</v>
+        <v>0.1675801138065289</v>
       </c>
       <c r="K25">
-        <v>0.581</v>
+        <v>0.722</v>
       </c>
       <c r="L25">
-        <v>0.1271334792122538</v>
+        <v>0.1663594470046083</v>
       </c>
       <c r="M25">
-        <v>1.64</v>
+        <v>0.421</v>
       </c>
       <c r="N25">
-        <v>0.04672364672364672</v>
+        <v>0.03422764227642276</v>
       </c>
       <c r="O25">
-        <v>2.822719449225473</v>
+        <v>0.5831024930747922</v>
       </c>
       <c r="P25">
-        <v>1.64</v>
+        <v>0.421</v>
       </c>
       <c r="Q25">
-        <v>0.04672364672364672</v>
+        <v>0.03422764227642276</v>
       </c>
       <c r="R25">
-        <v>2.822719449225473</v>
+        <v>0.5831024930747922</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3523,73 +3499,73 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>7.21</v>
+        <v>5.15</v>
       </c>
       <c r="V25">
-        <v>0.2054131054131054</v>
+        <v>0.4186991869918699</v>
       </c>
       <c r="W25">
-        <v>0.04006896551724138</v>
+        <v>0.07148514851485148</v>
       </c>
       <c r="X25">
-        <v>0.07703170382728568</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y25">
-        <v>-0.0369627383100443</v>
+        <v>-0.05128829689182959</v>
       </c>
       <c r="Z25">
-        <v>0.7052469135802469</v>
+        <v>0.9475982532751092</v>
       </c>
       <c r="AA25">
-        <v>0.1095679012345679</v>
+        <v>0.1587986231267108</v>
       </c>
       <c r="AB25">
-        <v>0.07698158097686966</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC25">
-        <v>0.03258632025769823</v>
+        <v>0.03602517772002971</v>
       </c>
       <c r="AD25">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>-7.163</v>
+        <v>-5.15</v>
       </c>
       <c r="AH25">
-        <v>0.001337240731783652</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>0.003023091271627967</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <v>-0.2563983248022336</v>
+        <v>-0.7202797202797203</v>
       </c>
       <c r="AK25">
-        <v>-0.8591819599376275</v>
+        <v>-1.458923512747876</v>
       </c>
       <c r="AL25">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="AM25">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="AN25">
-        <v>0.02848484848484849</v>
+        <v>0</v>
       </c>
       <c r="AO25">
-        <v>284</v>
+        <v>87.36363636363636</v>
       </c>
       <c r="AP25">
-        <v>-4.341212121212122</v>
+        <v>-5.049019607843137</v>
       </c>
       <c r="AQ25">
-        <v>284</v>
+        <v>87.36363636363636</v>
       </c>
     </row>
     <row r="26">
@@ -3600,7 +3576,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nitol Insurance Company Limited (DSE:NITOLINS)</t>
+          <t>Crystal Insurance Company Limited (DSE:CRYSTALINS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3608,47 +3584,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D26">
-        <v>-0.00915</v>
-      </c>
-      <c r="E26">
-        <v>0.128</v>
-      </c>
       <c r="G26">
-        <v>0.3584905660377358</v>
+        <v>1.009569377990431</v>
       </c>
       <c r="H26">
-        <v>0.3584905660377358</v>
+        <v>1.009569377990431</v>
       </c>
       <c r="I26">
-        <v>0.3224699828473413</v>
+        <v>0.7511961722488039</v>
       </c>
       <c r="J26">
-        <v>0.2271012006861063</v>
+        <v>0.7511961722488039</v>
       </c>
       <c r="K26">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="L26">
-        <v>0.2264150943396226</v>
+        <v>0.7177033492822967</v>
       </c>
       <c r="M26">
-        <v>0.397</v>
+        <v>0.399</v>
       </c>
       <c r="N26">
-        <v>0.01373702422145329</v>
+        <v>0.02541401273885351</v>
       </c>
       <c r="O26">
-        <v>0.3007575757575758</v>
+        <v>0.266</v>
       </c>
       <c r="P26">
-        <v>0.397</v>
+        <v>0.399</v>
       </c>
       <c r="Q26">
-        <v>0.01373702422145329</v>
+        <v>0.02541401273885351</v>
       </c>
       <c r="R26">
-        <v>0.3007575757575758</v>
+        <v>0.266</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3657,67 +3627,73 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>0.615</v>
+        <v>0.379</v>
       </c>
       <c r="V26">
-        <v>0.021280276816609</v>
+        <v>0.02414012738853503</v>
       </c>
       <c r="W26">
-        <v>0.1047619047619048</v>
+        <v>0.1442307692307692</v>
       </c>
       <c r="X26">
-        <v>0.07697577764364623</v>
+        <v>0.1230406093301246</v>
       </c>
       <c r="Y26">
-        <v>0.02778612711825854</v>
+        <v>0.02119015990064461</v>
       </c>
       <c r="Z26">
-        <v>0.4740993738310157</v>
+        <v>0.2085620197585071</v>
       </c>
       <c r="AA26">
-        <v>0.1076685370415549</v>
+        <v>0.1566709909190699</v>
       </c>
       <c r="AB26">
-        <v>0.07697577764364623</v>
+        <v>0.1227769030381793</v>
       </c>
       <c r="AC26">
-        <v>0.03069275939790862</v>
+        <v>0.03389408788089063</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AG26">
-        <v>-0.615</v>
+        <v>-0.305</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>0.004691264105490047</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>0.007794396460922687</v>
       </c>
       <c r="AJ26">
-        <v>-0.02174297330740675</v>
+        <v>-0.01981162715167262</v>
       </c>
       <c r="AK26">
-        <v>-0.04810324599139617</v>
+        <v>-0.03346132748217224</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>0.03814432989690721</v>
+      </c>
+      <c r="AO26">
+        <v>142.7272727272727</v>
       </c>
       <c r="AP26">
-        <v>-0.2928571428571428</v>
+        <v>-0.1572164948453608</v>
+      </c>
+      <c r="AQ26">
+        <v>142.7272727272727</v>
       </c>
     </row>
     <row r="27">
@@ -3728,7 +3704,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eastland Insurance Company Limited (DSE:EASTLAND)</t>
+          <t>Rupali Insurance Company Limited (DSE:RUPALIINS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3737,46 +3713,46 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0124</v>
+        <v>-0.0765</v>
       </c>
       <c r="E27">
-        <v>0.0155</v>
+        <v>0.0551</v>
       </c>
       <c r="G27">
-        <v>0.3362218370883882</v>
+        <v>0.5736607142857142</v>
       </c>
       <c r="H27">
-        <v>0.3362218370883882</v>
+        <v>0.5736607142857142</v>
       </c>
       <c r="I27">
-        <v>0.341421143847487</v>
+        <v>0.3950892857142857</v>
       </c>
       <c r="J27">
-        <v>0.2612320988780444</v>
+        <v>0.3300982671174979</v>
       </c>
       <c r="K27">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="L27">
-        <v>0.2010398613518198</v>
+        <v>0.3147321428571428</v>
       </c>
       <c r="M27">
-        <v>0.865</v>
+        <v>0.761</v>
       </c>
       <c r="N27">
-        <v>0.02270341207349081</v>
+        <v>0.03843434343434343</v>
       </c>
       <c r="O27">
-        <v>0.7456896551724138</v>
+        <v>0.5397163120567376</v>
       </c>
       <c r="P27">
-        <v>0.865</v>
+        <v>0.761</v>
       </c>
       <c r="Q27">
-        <v>0.02270341207349081</v>
+        <v>0.03843434343434343</v>
       </c>
       <c r="R27">
-        <v>0.7456896551724138</v>
+        <v>0.5397163120567376</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3785,31 +3761,31 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>5.53</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="V27">
-        <v>0.1451443569553806</v>
+        <v>0.4606060606060606</v>
       </c>
       <c r="W27">
-        <v>0.05771144278606964</v>
+        <v>0.06409090909090909</v>
       </c>
       <c r="X27">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y27">
-        <v>-0.01926433485757659</v>
+        <v>-0.05868253631577199</v>
       </c>
       <c r="Z27">
-        <v>0.3952054794520548</v>
+        <v>0.4480000000000001</v>
       </c>
       <c r="AA27">
-        <v>0.1032403568853641</v>
+        <v>0.1478840236686391</v>
       </c>
       <c r="AB27">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC27">
-        <v>0.02626457924171786</v>
+        <v>0.02511057826195799</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -3821,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>-5.53</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -3830,28 +3806,22 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>-0.1697881486030089</v>
+        <v>-0.8539325842696627</v>
       </c>
       <c r="AK27">
-        <v>-0.3077351140790206</v>
+        <v>-0.9230769230769229</v>
       </c>
       <c r="AL27">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AN27">
         <v>0</v>
       </c>
-      <c r="AO27">
-        <v>4.925</v>
-      </c>
       <c r="AP27">
-        <v>-2.821428571428572</v>
-      </c>
-      <c r="AQ27">
-        <v>4.925</v>
+        <v>-5.094972067039105</v>
       </c>
     </row>
     <row r="28">
@@ -3862,7 +3832,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mercantile Insurance Company Limited (DSE:MERCINS)</t>
+          <t>Paramount Insurance Company Limited (DSE:PARAMOUNT)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3871,46 +3841,46 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0437</v>
+        <v>0.198</v>
       </c>
       <c r="E28">
-        <v>0.0101</v>
+        <v>0.199</v>
       </c>
       <c r="G28">
-        <v>0.2748815165876777</v>
+        <v>0.6085714285714285</v>
       </c>
       <c r="H28">
-        <v>0.2748815165876777</v>
+        <v>0.6085714285714285</v>
       </c>
       <c r="I28">
-        <v>0.2535545023696683</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="J28">
-        <v>0.1999731735670214</v>
+        <v>0.2251428571428572</v>
       </c>
       <c r="K28">
-        <v>0.838</v>
+        <v>0.787</v>
       </c>
       <c r="L28">
-        <v>0.1985781990521327</v>
+        <v>0.2248571428571429</v>
       </c>
       <c r="M28">
-        <v>0.863</v>
+        <v>0.404</v>
       </c>
       <c r="N28">
-        <v>0.03424603174603175</v>
+        <v>0.02295454545454545</v>
       </c>
       <c r="O28">
-        <v>1.029832935560859</v>
+        <v>0.5133418043202033</v>
       </c>
       <c r="P28">
-        <v>0.863</v>
+        <v>0.404</v>
       </c>
       <c r="Q28">
-        <v>0.03424603174603175</v>
+        <v>0.02295454545454545</v>
       </c>
       <c r="R28">
-        <v>1.029832935560859</v>
+        <v>0.5133418043202033</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3919,31 +3889,31 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>12.1</v>
+        <v>5.74</v>
       </c>
       <c r="V28">
-        <v>0.4801587301587302</v>
+        <v>0.3261363636363636</v>
       </c>
       <c r="W28">
-        <v>0.08481781376518217</v>
+        <v>0.06450819672131149</v>
       </c>
       <c r="X28">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y28">
-        <v>0.007842036121535945</v>
+        <v>-0.05826524868536959</v>
       </c>
       <c r="Z28">
-        <v>-2.604938271604939</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="AA28">
-        <v>-0.5209177731190313</v>
+        <v>0.1279220779220779</v>
       </c>
       <c r="AB28">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC28">
-        <v>-0.5978935507626776</v>
+        <v>0.005148632515396864</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -3955,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="AG28">
-        <v>-12.1</v>
+        <v>-5.74</v>
       </c>
       <c r="AH28">
         <v>0</v>
@@ -3964,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AJ28">
-        <v>-0.9236641221374046</v>
+        <v>-0.4839797639123102</v>
       </c>
       <c r="AK28">
-        <v>5.127118644067798</v>
+        <v>-1.205882352941177</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3979,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>-10.9009009009009</v>
+        <v>-4.592000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -3990,7 +3960,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Standard Insurance Limited (DSE:STANDARINS)</t>
+          <t>Green Delta Insurance Company Limited (DSE:GREENDELT)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3998,41 +3968,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D29">
+        <v>0.0473</v>
+      </c>
+      <c r="E29">
+        <v>0.278</v>
+      </c>
       <c r="G29">
-        <v>0.252072968490879</v>
+        <v>0.5778546712802768</v>
       </c>
       <c r="H29">
-        <v>0.252072968490879</v>
+        <v>0.5778546712802768</v>
       </c>
       <c r="I29">
-        <v>0.2653399668325042</v>
+        <v>0.3910034602076125</v>
       </c>
       <c r="J29">
-        <v>0.2129353233830846</v>
+        <v>0.2560320734628693</v>
       </c>
       <c r="K29">
-        <v>1.28</v>
+        <v>6.82</v>
       </c>
       <c r="L29">
-        <v>0.2122719734660033</v>
+        <v>0.2359861591695502</v>
       </c>
       <c r="M29">
-        <v>0.622</v>
+        <v>3.39</v>
       </c>
       <c r="N29">
-        <v>0.01607235142118863</v>
+        <v>0.05347003154574133</v>
       </c>
       <c r="O29">
-        <v>0.4859375</v>
+        <v>0.4970674486803519</v>
       </c>
       <c r="P29">
-        <v>0.622</v>
+        <v>3.39</v>
       </c>
       <c r="Q29">
-        <v>0.01607235142118863</v>
+        <v>0.05347003154574133</v>
       </c>
       <c r="R29">
-        <v>0.4859375</v>
+        <v>0.4970674486803519</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4041,31 +4017,31 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>13</v>
+        <v>16.4</v>
       </c>
       <c r="V29">
-        <v>0.3359173126614987</v>
+        <v>0.2586750788643533</v>
       </c>
       <c r="W29">
-        <v>0.1329179646936656</v>
+        <v>0.08399014778325123</v>
       </c>
       <c r="X29">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y29">
-        <v>0.0559421870500194</v>
+        <v>-0.03878329762342984</v>
       </c>
       <c r="Z29">
-        <v>-2.778801843317972</v>
+        <v>0.4594594594594594</v>
       </c>
       <c r="AA29">
-        <v>-0.591705069124424</v>
+        <v>0.1176363580775345</v>
       </c>
       <c r="AB29">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC29">
-        <v>-0.6686808467680703</v>
+        <v>-0.005137087329146528</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4077,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="AG29">
-        <v>-13</v>
+        <v>-16.4</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -4086,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="AJ29">
-        <v>-0.5058365758754864</v>
+        <v>-0.3489361702127659</v>
       </c>
       <c r="AK29">
-        <v>4.642857142857141</v>
+        <v>-0.3241106719367589</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -4101,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>-7.926829268292684</v>
+        <v>-1.378151260504201</v>
       </c>
     </row>
     <row r="30">
@@ -4112,7 +4088,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Islami Insurance Bangladesh Limited (DSE:ISLAMIINS)</t>
+          <t>Eastland Insurance Company Limited (DSE:EASTLAND)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4121,46 +4097,46 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.145</v>
+        <v>0.0246</v>
       </c>
       <c r="E30">
-        <v>0.279</v>
+        <v>-0.0358</v>
       </c>
       <c r="G30">
-        <v>0.1768368617683686</v>
+        <v>0.3232758620689655</v>
       </c>
       <c r="H30">
-        <v>0.1768368617683686</v>
+        <v>0.3232758620689655</v>
       </c>
       <c r="I30">
-        <v>0.2179327521793275</v>
+        <v>0.3089080459770115</v>
       </c>
       <c r="J30">
-        <v>0.1673366687786298</v>
+        <v>0.2346312798656851</v>
       </c>
       <c r="K30">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="L30">
-        <v>0.1631382316313823</v>
+        <v>0.1939655172413793</v>
       </c>
       <c r="M30">
-        <v>0.21</v>
+        <v>0.806</v>
       </c>
       <c r="N30">
-        <v>0.006687898089171975</v>
+        <v>0.04050251256281408</v>
       </c>
       <c r="O30">
-        <v>0.1603053435114504</v>
+        <v>0.597037037037037</v>
       </c>
       <c r="P30">
-        <v>0.21</v>
+        <v>0.806</v>
       </c>
       <c r="Q30">
-        <v>0.006687898089171975</v>
+        <v>0.04050251256281408</v>
       </c>
       <c r="R30">
-        <v>0.1603053435114504</v>
+        <v>0.597037037037037</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4169,31 +4145,31 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>10.2</v>
+        <v>4.37</v>
       </c>
       <c r="V30">
-        <v>0.3248407643312102</v>
+        <v>0.2195979899497488</v>
       </c>
       <c r="W30">
-        <v>0.191800878477306</v>
+        <v>0.0574468085106383</v>
       </c>
       <c r="X30">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="Y30">
-        <v>0.1148251008336598</v>
+        <v>-0.06532663689604276</v>
       </c>
       <c r="Z30">
-        <v>-6.58196721311475</v>
+        <v>0.3873121869782972</v>
       </c>
       <c r="AA30">
-        <v>-1.101404467452785</v>
+        <v>0.09087555413829541</v>
       </c>
       <c r="AB30">
-        <v>0.07697577764364623</v>
+        <v>0.1227734454066811</v>
       </c>
       <c r="AC30">
-        <v>-1.178380245096431</v>
+        <v>-0.03189789126838566</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4205,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>-10.2</v>
+        <v>-4.37</v>
       </c>
       <c r="AH30">
         <v>0</v>
@@ -4214,28 +4190,796 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>-0.4811320754716981</v>
+        <v>-0.2813908564069543</v>
       </c>
       <c r="AK30">
-        <v>4.513274336283188</v>
+        <v>-0.3328255902513328</v>
       </c>
       <c r="AL30">
-        <v>0.007</v>
+        <v>0.348</v>
       </c>
       <c r="AM30">
-        <v>0.007</v>
+        <v>0.348</v>
       </c>
       <c r="AN30">
         <v>0</v>
       </c>
       <c r="AO30">
-        <v>250</v>
+        <v>6.17816091954023</v>
       </c>
       <c r="AP30">
-        <v>-5.513513513513513</v>
+        <v>-2.071090047393365</v>
       </c>
       <c r="AQ30">
-        <v>250</v>
+        <v>6.17816091954023</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Republic Insurance Company Limited (DSE:REPUBLIC)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.04940000000000001</v>
+      </c>
+      <c r="E31">
+        <v>0.0447</v>
+      </c>
+      <c r="G31">
+        <v>0.2948207171314741</v>
+      </c>
+      <c r="H31">
+        <v>0.2948207171314741</v>
+      </c>
+      <c r="I31">
+        <v>0.2290836653386454</v>
+      </c>
+      <c r="J31">
+        <v>0.1469164663659412</v>
+      </c>
+      <c r="K31">
+        <v>0.775</v>
+      </c>
+      <c r="L31">
+        <v>0.1543824701195219</v>
+      </c>
+      <c r="M31">
+        <v>0.462</v>
+      </c>
+      <c r="N31">
+        <v>0.02733727810650888</v>
+      </c>
+      <c r="O31">
+        <v>0.5961290322580646</v>
+      </c>
+      <c r="P31">
+        <v>0.462</v>
+      </c>
+      <c r="Q31">
+        <v>0.02733727810650888</v>
+      </c>
+      <c r="R31">
+        <v>0.5961290322580646</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0.736</v>
+      </c>
+      <c r="V31">
+        <v>0.04355029585798817</v>
+      </c>
+      <c r="W31">
+        <v>0.08115183246073299</v>
+      </c>
+      <c r="X31">
+        <v>0.1232161693111624</v>
+      </c>
+      <c r="Y31">
+        <v>-0.04206433685042946</v>
+      </c>
+      <c r="Z31">
+        <v>0.5733211512105983</v>
+      </c>
+      <c r="AA31">
+        <v>0.08423031762871455</v>
+      </c>
+      <c r="AB31">
+        <v>0.1227990365750236</v>
+      </c>
+      <c r="AC31">
+        <v>-0.03856871894630901</v>
+      </c>
+      <c r="AD31">
+        <v>0.132</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0.132</v>
+      </c>
+      <c r="AG31">
+        <v>-0.604</v>
+      </c>
+      <c r="AH31">
+        <v>0.007750117426021607</v>
+      </c>
+      <c r="AI31">
+        <v>0.01487826871055005</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.03706431026018655</v>
+      </c>
+      <c r="AK31">
+        <v>-0.07423795476892821</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agrani Insurance Company Limited (DSE:AGRANINS)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>-0.0125</v>
+      </c>
+      <c r="E32">
+        <v>-0.096</v>
+      </c>
+      <c r="G32">
+        <v>0.2384905660377359</v>
+      </c>
+      <c r="H32">
+        <v>0.2384905660377359</v>
+      </c>
+      <c r="I32">
+        <v>0.2116981132075472</v>
+      </c>
+      <c r="J32">
+        <v>0.1123145312654351</v>
+      </c>
+      <c r="K32">
+        <v>0.36</v>
+      </c>
+      <c r="L32">
+        <v>0.1358490566037736</v>
+      </c>
+      <c r="M32">
+        <v>0.204</v>
+      </c>
+      <c r="N32">
+        <v>0.01789473684210526</v>
+      </c>
+      <c r="O32">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="P32">
+        <v>0.204</v>
+      </c>
+      <c r="Q32">
+        <v>0.01789473684210526</v>
+      </c>
+      <c r="R32">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>3.87</v>
+      </c>
+      <c r="V32">
+        <v>0.3394736842105263</v>
+      </c>
+      <c r="W32">
+        <v>0.05564142194744977</v>
+      </c>
+      <c r="X32">
+        <v>0.1242998837596986</v>
+      </c>
+      <c r="Y32">
+        <v>-0.06865846181224881</v>
+      </c>
+      <c r="Z32">
+        <v>0.7391910739191075</v>
+      </c>
+      <c r="AA32">
+        <v>0.0830218989828182</v>
+      </c>
+      <c r="AB32">
+        <v>0.1228600367721276</v>
+      </c>
+      <c r="AC32">
+        <v>-0.03983813778930941</v>
+      </c>
+      <c r="AD32">
+        <v>0.307</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0.307</v>
+      </c>
+      <c r="AG32">
+        <v>-3.563</v>
+      </c>
+      <c r="AH32">
+        <v>0.02622362688989493</v>
+      </c>
+      <c r="AI32">
+        <v>0.03967946232389815</v>
+      </c>
+      <c r="AJ32">
+        <v>-0.4546382544340947</v>
+      </c>
+      <c r="AK32">
+        <v>-0.9213860874062583</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0.4857594936708861</v>
+      </c>
+      <c r="AP32">
+        <v>-5.637658227848101</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nitol Insurance Company Limited (DSE:NITOLINS)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>-0.0556</v>
+      </c>
+      <c r="E33">
+        <v>-0.0239</v>
+      </c>
+      <c r="G33">
+        <v>0.4605263157894737</v>
+      </c>
+      <c r="H33">
+        <v>0.4605263157894737</v>
+      </c>
+      <c r="I33">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="J33">
+        <v>0.1988169966199904</v>
+      </c>
+      <c r="K33">
+        <v>0.91</v>
+      </c>
+      <c r="L33">
+        <v>0.199561403508772</v>
+      </c>
+      <c r="M33">
+        <v>0.527</v>
+      </c>
+      <c r="N33">
+        <v>0.03233128834355829</v>
+      </c>
+      <c r="O33">
+        <v>0.5791208791208792</v>
+      </c>
+      <c r="P33">
+        <v>0.527</v>
+      </c>
+      <c r="Q33">
+        <v>0.03233128834355829</v>
+      </c>
+      <c r="R33">
+        <v>0.5791208791208792</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0.225</v>
+      </c>
+      <c r="V33">
+        <v>0.01380368098159509</v>
+      </c>
+      <c r="W33">
+        <v>0.06791044776119404</v>
+      </c>
+      <c r="X33">
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="Y33">
+        <v>-0.05486299764548704</v>
+      </c>
+      <c r="Z33">
+        <v>0.3566679702776691</v>
+      </c>
+      <c r="AA33">
+        <v>0.07091165464115416</v>
+      </c>
+      <c r="AB33">
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="AC33">
+        <v>-0.05186179076552691</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>-0.225</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>-0.01399688958009331</v>
+      </c>
+      <c r="AK33">
+        <v>-0.0196078431372549</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>-0.1785714285714286</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Phoenix Insurance Company Limited (DSE:PHENIXINS)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>-0.0452</v>
+      </c>
+      <c r="E34">
+        <v>-0.0484</v>
+      </c>
+      <c r="G34">
+        <v>0.3371040723981901</v>
+      </c>
+      <c r="H34">
+        <v>0.3371040723981901</v>
+      </c>
+      <c r="I34">
+        <v>0.2398190045248869</v>
+      </c>
+      <c r="J34">
+        <v>0.1859147328656233</v>
+      </c>
+      <c r="K34">
+        <v>0.845</v>
+      </c>
+      <c r="L34">
+        <v>0.1911764705882353</v>
+      </c>
+      <c r="M34">
+        <v>0.607</v>
+      </c>
+      <c r="N34">
+        <v>0.04073825503355705</v>
+      </c>
+      <c r="O34">
+        <v>0.7183431952662722</v>
+      </c>
+      <c r="P34">
+        <v>0.607</v>
+      </c>
+      <c r="Q34">
+        <v>0.04073825503355705</v>
+      </c>
+      <c r="R34">
+        <v>0.7183431952662722</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>5.02</v>
+      </c>
+      <c r="V34">
+        <v>0.3369127516778523</v>
+      </c>
+      <c r="W34">
+        <v>0.04246231155778895</v>
+      </c>
+      <c r="X34">
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="Y34">
+        <v>-0.08031113384889213</v>
+      </c>
+      <c r="Z34">
+        <v>0.3012951601908657</v>
+      </c>
+      <c r="AA34">
+        <v>0.05601520922058999</v>
+      </c>
+      <c r="AB34">
+        <v>0.1227734454066811</v>
+      </c>
+      <c r="AC34">
+        <v>-0.06675823618609109</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>-5.02</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>-0.5080971659919028</v>
+      </c>
+      <c r="AK34">
+        <v>-0.5080971659919028</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>-4.183333333333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dhaka Insurance Limited (DSE:DHAKAINS)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.113</v>
+      </c>
+      <c r="E35">
+        <v>-0.197</v>
+      </c>
+      <c r="G35">
+        <v>0.3387096774193549</v>
+      </c>
+      <c r="H35">
+        <v>0.3387096774193549</v>
+      </c>
+      <c r="I35">
+        <v>0.2078341013824885</v>
+      </c>
+      <c r="J35">
+        <v>0.1039170506912442</v>
+      </c>
+      <c r="K35">
+        <v>0.237</v>
+      </c>
+      <c r="L35">
+        <v>0.05460829493087557</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>0.05401069518716578</v>
+      </c>
+      <c r="O35">
+        <v>4.261603375527426</v>
+      </c>
+      <c r="P35">
+        <v>1.01</v>
+      </c>
+      <c r="Q35">
+        <v>0.05401069518716578</v>
+      </c>
+      <c r="R35">
+        <v>4.261603375527426</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>6.6</v>
+      </c>
+      <c r="V35">
+        <v>0.3529411764705882</v>
+      </c>
+      <c r="W35">
+        <v>0.01529032258064516</v>
+      </c>
+      <c r="X35">
+        <v>0.1228401302015628</v>
+      </c>
+      <c r="Y35">
+        <v>-0.1075498076209177</v>
+      </c>
+      <c r="Z35">
+        <v>0.5205709487825357</v>
+      </c>
+      <c r="AA35">
+        <v>0.05409619767302387</v>
+      </c>
+      <c r="AB35">
+        <v>0.122777325590237</v>
+      </c>
+      <c r="AC35">
+        <v>-0.06868112791721316</v>
+      </c>
+      <c r="AD35">
+        <v>0.022</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0.022</v>
+      </c>
+      <c r="AG35">
+        <v>-6.577999999999999</v>
+      </c>
+      <c r="AH35">
+        <v>0.001175088131609871</v>
+      </c>
+      <c r="AI35">
+        <v>0.001651403693139168</v>
+      </c>
+      <c r="AJ35">
+        <v>-0.542649727767695</v>
+      </c>
+      <c r="AK35">
+        <v>-0.9785778042249328</v>
+      </c>
+      <c r="AL35">
+        <v>0.004</v>
+      </c>
+      <c r="AM35">
+        <v>0.004</v>
+      </c>
+      <c r="AN35">
+        <v>0.0205607476635514</v>
+      </c>
+      <c r="AO35">
+        <v>225.5</v>
+      </c>
+      <c r="AP35">
+        <v>-6.147663551401868</v>
+      </c>
+      <c r="AQ35">
+        <v>225.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Union Insurance Co. Ltd. (DSE:UNIONINS)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="H36">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="I36">
+        <v>-0.002487562189054726</v>
+      </c>
+      <c r="J36">
+        <v>-0.002487562189054726</v>
+      </c>
+      <c r="K36">
+        <v>-0.008</v>
+      </c>
+      <c r="L36">
+        <v>-0.001326699834162521</v>
+      </c>
+      <c r="M36">
+        <v>0.242</v>
+      </c>
+      <c r="N36">
+        <v>0.01375</v>
+      </c>
+      <c r="O36">
+        <v>-30.25</v>
+      </c>
+      <c r="P36">
+        <v>0.242</v>
+      </c>
+      <c r="Q36">
+        <v>0.01375</v>
+      </c>
+      <c r="R36">
+        <v>-30.25</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>2.83</v>
+      </c>
+      <c r="V36">
+        <v>0.1607954545454545</v>
+      </c>
+      <c r="W36">
+        <v>-0.001342281879194631</v>
+      </c>
+      <c r="X36">
+        <v>0.1234014570402978</v>
+      </c>
+      <c r="Y36">
+        <v>-0.1247437389194924</v>
+      </c>
+      <c r="Z36">
+        <v>1.563391236712471</v>
+      </c>
+      <c r="AA36">
+        <v>-0.00388903292714545</v>
+      </c>
+      <c r="AB36">
+        <v>0.1228096295629157</v>
+      </c>
+      <c r="AC36">
+        <v>-0.1266986624900612</v>
+      </c>
+      <c r="AD36">
+        <v>0.195</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0.195</v>
+      </c>
+      <c r="AG36">
+        <v>-2.635</v>
+      </c>
+      <c r="AH36">
+        <v>0.01095813430738972</v>
+      </c>
+      <c r="AI36">
+        <v>0.02245250431778929</v>
+      </c>
+      <c r="AJ36">
+        <v>-0.1760775141997995</v>
+      </c>
+      <c r="AK36">
+        <v>-0.4500426985482494</v>
+      </c>
+      <c r="AL36">
+        <v>0.045</v>
+      </c>
+      <c r="AM36">
+        <v>0.045</v>
+      </c>
+      <c r="AN36">
+        <v>0.7442748091603053</v>
+      </c>
+      <c r="AO36">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AP36">
+        <v>-10.05725190839695</v>
+      </c>
+      <c r="AQ36">
+        <v>-0.3333333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ36"/>
+  <dimension ref="A1:AQ38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0823</v>
+        <v>0.0863</v>
       </c>
       <c r="E2">
-        <v>0.08929999999999999</v>
+        <v>0.04865</v>
       </c>
       <c r="G2">
-        <v>0.3792546248368367</v>
+        <v>0.3341402651123437</v>
       </c>
       <c r="H2">
-        <v>0.3792546248368367</v>
+        <v>0.3341402651123437</v>
       </c>
       <c r="I2">
-        <v>0.284160777782779</v>
+        <v>0.2773808404625364</v>
       </c>
       <c r="J2">
-        <v>0.2130702221822675</v>
+        <v>0.2080421798016879</v>
       </c>
       <c r="K2">
-        <v>44.202</v>
+        <v>38.298</v>
       </c>
       <c r="L2">
-        <v>0.1989557546023316</v>
+        <v>0.1800225627526558</v>
       </c>
       <c r="M2">
-        <v>20.846</v>
+        <v>19.982</v>
       </c>
       <c r="N2">
-        <v>0.03033027789902517</v>
+        <v>0.02615102735244078</v>
       </c>
       <c r="O2">
-        <v>0.4716076195647256</v>
+        <v>0.5217504830539453</v>
       </c>
       <c r="P2">
-        <v>20.846</v>
+        <v>19.982</v>
       </c>
       <c r="Q2">
-        <v>0.03033027789902517</v>
+        <v>0.02615102735244078</v>
       </c>
       <c r="R2">
-        <v>0.4716076195647256</v>
+        <v>0.5217504830539453</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>232.56</v>
+        <v>205.592</v>
       </c>
       <c r="V2">
-        <v>0.3383675250982104</v>
+        <v>0.2690642586048946</v>
       </c>
       <c r="W2">
-        <v>0.09127033492822967</v>
+        <v>0.08427795402644642</v>
       </c>
       <c r="X2">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y2">
-        <v>-0.0315031104784514</v>
+        <v>-0.02837009281717633</v>
       </c>
       <c r="Z2">
-        <v>0.943873974534903</v>
+        <v>1.011015958407391</v>
       </c>
       <c r="AA2">
-        <v>0.2427919072649095</v>
+        <v>0.2945421445563031</v>
       </c>
       <c r="AB2">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC2">
-        <v>0.1200184618582284</v>
+        <v>0.1818940977126804</v>
       </c>
       <c r="AD2">
-        <v>1.922</v>
+        <v>2.01</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.922</v>
+        <v>2.01</v>
       </c>
       <c r="AG2">
-        <v>-230.638</v>
+        <v>-203.582</v>
       </c>
       <c r="AH2">
-        <v>0.002788651552039836</v>
+        <v>0.002623644124211927</v>
       </c>
       <c r="AI2">
-        <v>0.004420707865271912</v>
+        <v>0.004812642164491799</v>
       </c>
       <c r="AJ2">
-        <v>-0.5050518764425331</v>
+        <v>-0.3632033226408429</v>
       </c>
       <c r="AK2">
-        <v>-1.140575237869167</v>
+        <v>-0.9600298031670581</v>
       </c>
       <c r="AL2">
-        <v>0.6669999999999999</v>
+        <v>0.393</v>
       </c>
       <c r="AM2">
-        <v>0.6669999999999999</v>
+        <v>0.393</v>
       </c>
       <c r="AN2">
-        <v>0.02888357903911756</v>
+        <v>0.03140477790103589</v>
       </c>
       <c r="AO2">
-        <v>94.65067466266868</v>
+        <v>150.1526717557252</v>
       </c>
       <c r="AP2">
-        <v>-3.465999428940685</v>
+        <v>-3.180819649078949</v>
       </c>
       <c r="AQ2">
-        <v>94.65067466266868</v>
+        <v>150.1526717557252</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Provati Insurance Company Limited (DSE:PROVATIINS)</t>
+          <t>Express Insurance Limited (DSE:EIL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,104 +721,107 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.19</v>
-      </c>
-      <c r="E3">
-        <v>0.14</v>
-      </c>
       <c r="G3">
-        <v>0.2198019801980198</v>
+        <v>0.8651685393258427</v>
       </c>
       <c r="H3">
-        <v>0.2198019801980198</v>
+        <v>0.8651685393258427</v>
       </c>
       <c r="I3">
-        <v>0.1178217821782178</v>
+        <v>0.7415730337078652</v>
       </c>
       <c r="J3">
-        <v>0.09789026402640263</v>
+        <v>0.3707865168539326</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.379</v>
       </c>
       <c r="L3">
-        <v>0.09900990099009901</v>
+        <v>0.2129213483146067</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.599</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0262719298245614</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.580474934036939</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.599</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0262719298245614</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.580474934036939</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>7.61</v>
+        <v>10.9</v>
       </c>
       <c r="V3">
-        <v>0.3294372294372294</v>
+        <v>0.4780701754385965</v>
       </c>
       <c r="W3">
-        <v>0.1164144353899884</v>
+        <v>0.03007936507936508</v>
       </c>
       <c r="X3">
-        <v>0.1246334026942277</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y3">
-        <v>-0.008218967304239391</v>
+        <v>-0.08256868176425766</v>
       </c>
       <c r="AB3">
-        <v>0.1227968620151247</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AD3">
-        <v>0.758</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.758</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-6.852</v>
+        <v>-10.9</v>
       </c>
       <c r="AH3">
-        <v>0.0317713136054992</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.08857209628417854</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.4217134416543574</v>
+        <v>-0.9159663865546218</v>
       </c>
       <c r="AK3">
-        <v>-7.227848101265827</v>
+        <v>-27.24999999999998</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AN3">
-        <v>0.5742424242424242</v>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>132</v>
       </c>
       <c r="AP3">
-        <v>-5.19090909090909</v>
+        <v>-7.517241379310345</v>
+      </c>
+      <c r="AQ3">
+        <v>132</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bangladesh National Insurance Company Limited (DSE:BNICL)</t>
+          <t>Sena Kalyan Insurance Company Limited (DSE:SKICL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,68 +840,59 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.161</v>
-      </c>
-      <c r="E4">
-        <v>0.191</v>
-      </c>
       <c r="G4">
-        <v>0.2410986775178026</v>
+        <v>0.3122065727699531</v>
       </c>
       <c r="H4">
-        <v>0.2410986775178026</v>
+        <v>0.3122065727699531</v>
       </c>
       <c r="I4">
-        <v>0.202441505595117</v>
+        <v>0.3075117370892019</v>
       </c>
       <c r="J4">
-        <v>0.1660429318618535</v>
+        <v>0.2619630061068164</v>
       </c>
       <c r="K4">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="L4">
-        <v>0.1648016276703967</v>
+        <v>0.2652582159624413</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.436</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02213197969543147</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.3858407079646018</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.436</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02213197969543147</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.3858407079646018</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.642570281124498</v>
-      </c>
-      <c r="W4">
-        <v>0.1572815533980582</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.1227734454066811</v>
-      </c>
-      <c r="Y4">
-        <v>0.03450810799137717</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AB4">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -910,37 +904,25 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
       <c r="AJ4">
-        <v>-1.797752808988764</v>
-      </c>
-      <c r="AK4">
-        <v>3.478260869565218</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
-      <c r="AO4">
-        <v>153.0769230769231</v>
-      </c>
       <c r="AP4">
-        <v>-7.476635514018692</v>
-      </c>
-      <c r="AQ4">
-        <v>153.0769230769231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sena Kalyan Insurance Company Limited (DSE:SKICL)</t>
+          <t>Desh General Insurance Company Limited (DSE:DGIC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -959,41 +941,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.263</v>
+      </c>
+      <c r="E5">
+        <v>0.174</v>
+      </c>
       <c r="G5">
-        <v>0.3425925925925926</v>
+        <v>0.1907582938388626</v>
       </c>
       <c r="H5">
-        <v>0.3425925925925926</v>
+        <v>0.1907582938388626</v>
       </c>
       <c r="I5">
-        <v>0.3287037037037037</v>
+        <v>0.1677725118483412</v>
       </c>
       <c r="J5">
-        <v>0.3008718572587185</v>
+        <v>0.1059208945770634</v>
       </c>
       <c r="K5">
-        <v>1.25</v>
+        <v>0.411</v>
       </c>
       <c r="L5">
-        <v>0.2893518518518519</v>
+        <v>0.09739336492890996</v>
       </c>
       <c r="M5">
-        <v>0.184</v>
+        <v>0.388</v>
       </c>
       <c r="N5">
-        <v>0.008214285714285714</v>
+        <v>0.03007751937984496</v>
       </c>
       <c r="O5">
-        <v>0.1472</v>
+        <v>0.9440389294403894</v>
       </c>
       <c r="P5">
-        <v>0.184</v>
+        <v>0.388</v>
       </c>
       <c r="Q5">
-        <v>0.008214285714285714</v>
+        <v>0.03007751937984496</v>
       </c>
       <c r="R5">
-        <v>0.1472</v>
+        <v>0.9440389294403894</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AB5">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1032,16 +1020,22 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>13.88235294117647</v>
+      </c>
       <c r="AP5">
         <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>13.88235294117647</v>
       </c>
     </row>
     <row r="6">
@@ -1052,7 +1046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sonar Bangla Insurance Limited (DSE:SONARBAINS)</t>
+          <t>Global Insurance Limited (DSE:GLOBALINS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1061,46 +1055,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.109</v>
+        <v>0.324</v>
       </c>
       <c r="E6">
-        <v>0.0852</v>
+        <v>0.278</v>
       </c>
       <c r="G6">
-        <v>0.2596439169139466</v>
+        <v>0.267022696929239</v>
       </c>
       <c r="H6">
-        <v>0.2596439169139466</v>
+        <v>0.267022696929239</v>
       </c>
       <c r="I6">
-        <v>0.2477744807121662</v>
+        <v>0.1032042723631509</v>
       </c>
       <c r="J6">
-        <v>0.1974151219700181</v>
+        <v>0.07350731649797071</v>
       </c>
       <c r="K6">
-        <v>1.18</v>
+        <v>0.501</v>
       </c>
       <c r="L6">
-        <v>0.1750741839762611</v>
+        <v>0.06688918558077436</v>
       </c>
       <c r="M6">
-        <v>0.722</v>
+        <v>0.409</v>
       </c>
       <c r="N6">
-        <v>0.03902702702702703</v>
+        <v>0.03220472440944882</v>
       </c>
       <c r="O6">
-        <v>0.611864406779661</v>
+        <v>0.8163672654690618</v>
       </c>
       <c r="P6">
-        <v>0.722</v>
+        <v>0.409</v>
       </c>
       <c r="Q6">
-        <v>0.03902702702702703</v>
+        <v>0.03220472440944882</v>
       </c>
       <c r="R6">
-        <v>0.611864406779661</v>
+        <v>0.8163672654690618</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1109,46 +1103,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>0.5244094488188977</v>
+      </c>
+      <c r="W6">
+        <v>0.09294990723562152</v>
       </c>
       <c r="X6">
-        <v>0.1227734454066811</v>
+        <v>0.1145000628215514</v>
+      </c>
+      <c r="Y6">
+        <v>-0.02155015558592986</v>
       </c>
       <c r="AB6">
-        <v>0.1227734454066811</v>
+        <v>0.1130230167469242</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>-6.205</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.03458760927404029</v>
+      </c>
+      <c r="AI6">
+        <v>0.08371665133394664</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>-0.9553502694380294</v>
+      </c>
+      <c r="AK6">
+        <v>5.065306122448981</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.5152887882219706</v>
+      </c>
+      <c r="AO6">
+        <v>257.6666666666667</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>-7.027180067950169</v>
+      </c>
+      <c r="AQ6">
+        <v>257.6666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -1159,7 +1171,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mercantile Insurance Company Limited (DSE:MERCINS)</t>
+          <t>Bangladesh National Insurance Company Limited (DSE:BNICL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1167,41 +1179,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.121</v>
+      </c>
+      <c r="E7">
+        <v>0.118</v>
+      </c>
       <c r="G7">
-        <v>0.3245033112582781</v>
+        <v>0.3021766965428938</v>
       </c>
       <c r="H7">
-        <v>0.3245033112582781</v>
+        <v>0.3021766965428938</v>
       </c>
       <c r="I7">
-        <v>0.2869757174392936</v>
+        <v>0.2432778489116517</v>
       </c>
       <c r="J7">
-        <v>0.2155707357772331</v>
+        <v>0.1806658130601793</v>
       </c>
       <c r="K7">
-        <v>0.949</v>
+        <v>1.41</v>
       </c>
       <c r="L7">
-        <v>0.2094922737306843</v>
+        <v>0.1805377720870679</v>
       </c>
       <c r="M7">
-        <v>0.428</v>
+        <v>1.53</v>
       </c>
       <c r="N7">
-        <v>0.0334375</v>
+        <v>0.06538461538461539</v>
       </c>
       <c r="O7">
-        <v>0.4510010537407798</v>
+        <v>1.085106382978724</v>
       </c>
       <c r="P7">
-        <v>0.428</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>0.0334375</v>
+        <v>0.06538461538461539</v>
       </c>
       <c r="R7">
-        <v>0.4510010537407798</v>
+        <v>1.085106382978724</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1210,22 +1228,22 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="V7">
-        <v>0.8671874999999999</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="W7">
-        <v>0.09743326488706365</v>
+        <v>0.1236842105263158</v>
       </c>
       <c r="X7">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y7">
-        <v>-0.02534018051961742</v>
+        <v>0.01103616368269304</v>
       </c>
       <c r="AB7">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1237,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-11.1</v>
+        <v>-13.2</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1246,22 +1264,28 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-6.529411764705878</v>
+        <v>-1.294117647058824</v>
       </c>
       <c r="AK7">
-        <v>4.911504424778761</v>
+        <v>3.963963963963964</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>126.6666666666667</v>
+      </c>
       <c r="AP7">
-        <v>-8.161764705882351</v>
+        <v>-6.470588235294117</v>
+      </c>
+      <c r="AQ7">
+        <v>126.6666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -1272,7 +1296,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Islami Commercial Insurance Company Limited (DSE:ICICL)</t>
+          <t>Islami Insurance Bangladesh Limited (DSE:ISLAMIINS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1280,41 +1304,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.308</v>
+      </c>
+      <c r="E8">
+        <v>0.199</v>
+      </c>
       <c r="G8">
-        <v>0.2228235294117647</v>
+        <v>0.5827586206896552</v>
       </c>
       <c r="H8">
-        <v>0.2228235294117647</v>
+        <v>0.5827586206896552</v>
       </c>
       <c r="I8">
-        <v>0.2447058823529412</v>
+        <v>0.5293103448275862</v>
       </c>
       <c r="J8">
-        <v>0.163929183323815</v>
+        <v>0.4392889504153033</v>
       </c>
       <c r="K8">
-        <v>0.6909999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="L8">
-        <v>0.1625882352941176</v>
+        <v>0.09827586206896551</v>
       </c>
       <c r="M8">
-        <v>0.553</v>
+        <v>0.546</v>
       </c>
       <c r="N8">
-        <v>0.04007246376811594</v>
+        <v>0.03102272727272727</v>
       </c>
       <c r="O8">
-        <v>0.800289435600579</v>
+        <v>0.4789473684210527</v>
       </c>
       <c r="P8">
-        <v>0.553</v>
+        <v>0.546</v>
       </c>
       <c r="Q8">
-        <v>0.04007246376811594</v>
+        <v>0.03102272727272727</v>
       </c>
       <c r="R8">
-        <v>0.800289435600579</v>
+        <v>0.4789473684210527</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1323,52 +1353,64 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>3.85</v>
+        <v>6.26</v>
       </c>
       <c r="V8">
-        <v>0.2789855072463768</v>
+        <v>0.3556818181818182</v>
+      </c>
+      <c r="W8">
+        <v>0.154054054054054</v>
       </c>
       <c r="X8">
-        <v>0.1227734454066811</v>
+        <v>0.1129212006987091</v>
+      </c>
+      <c r="Y8">
+        <v>0.04113285335534493</v>
       </c>
       <c r="AB8">
-        <v>0.1227734454066811</v>
+        <v>0.1126738262502357</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="AG8">
-        <v>-3.85</v>
+        <v>-6.167</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.005256316057197762</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.01234567901234568</v>
       </c>
       <c r="AJ8">
-        <v>-0.3869346733668341</v>
+        <v>-0.5394034811510539</v>
       </c>
       <c r="AK8">
-        <v>-1.332179930795848</v>
+        <v>-4.844461901021208</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>0.01478537360890302</v>
+      </c>
+      <c r="AO8">
+        <v>877.1428571428571</v>
       </c>
       <c r="AP8">
-        <v>-3.4375</v>
+        <v>-0.9804451510333863</v>
+      </c>
+      <c r="AQ8">
+        <v>877.1428571428571</v>
       </c>
     </row>
     <row r="9">
@@ -1379,7 +1421,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standard Insurance Limited (DSE:STANDARINS)</t>
+          <t>Agrani Insurance Company Limited (DSE:AGRANINS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1388,46 +1430,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.225</v>
+        <v>0.0328</v>
       </c>
       <c r="E9">
-        <v>0.0934</v>
+        <v>0.151</v>
       </c>
       <c r="G9">
-        <v>0.3674321503131524</v>
+        <v>0.4866920152091255</v>
       </c>
       <c r="H9">
-        <v>0.3674321503131524</v>
+        <v>0.4866920152091255</v>
       </c>
       <c r="I9">
-        <v>0.2881002087682672</v>
+        <v>0.4562737642585551</v>
       </c>
       <c r="J9">
-        <v>0.2341080955694734</v>
+        <v>0.3501901140684411</v>
       </c>
       <c r="K9">
-        <v>1.09</v>
+        <v>0.951</v>
       </c>
       <c r="L9">
-        <v>0.2275574112734864</v>
+        <v>0.3615969581749049</v>
       </c>
       <c r="M9">
-        <v>0.551</v>
+        <v>0.406</v>
       </c>
       <c r="N9">
-        <v>0.02727722772277228</v>
+        <v>0.03355371900826447</v>
       </c>
       <c r="O9">
-        <v>0.5055045871559634</v>
+        <v>0.4269190325972661</v>
       </c>
       <c r="P9">
-        <v>0.551</v>
+        <v>0.406</v>
       </c>
       <c r="Q9">
-        <v>0.02727722772277228</v>
+        <v>0.03355371900826447</v>
       </c>
       <c r="R9">
-        <v>0.5055045871559634</v>
+        <v>0.4269190325972661</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1436,64 +1478,46 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>0.5544554455445544</v>
-      </c>
-      <c r="W9">
-        <v>0.1068627450980392</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>0.1232869513395454</v>
-      </c>
-      <c r="Y9">
-        <v>-0.01642420624150621</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AB9">
-        <v>0.122780062569303</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AD9">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>-11.017</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>0.008978069960261003</v>
-      </c>
-      <c r="AI9">
-        <v>0.02032655781406198</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-1.199716868125885</v>
-      </c>
-      <c r="AK9">
-        <v>5.014565316340466</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>0.1211920529801324</v>
-      </c>
-      <c r="AO9">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>-7.296026490066224</v>
-      </c>
-      <c r="AQ9">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1504,7 +1528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Desh General Insurance Company Limited (DSE:DGIC)</t>
+          <t>Purabi General Insurance Company Limited (DSE:PURABIGEN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1513,46 +1537,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.191</v>
+        <v>0.106</v>
       </c>
       <c r="E10">
-        <v>0.302</v>
+        <v>0.00213</v>
       </c>
       <c r="G10">
-        <v>0.3517915309446255</v>
+        <v>0.7383720930232558</v>
       </c>
       <c r="H10">
-        <v>0.3517915309446255</v>
+        <v>0.7383720930232558</v>
       </c>
       <c r="I10">
-        <v>0.3110749185667753</v>
+        <v>0.5279069767441861</v>
       </c>
       <c r="J10">
-        <v>0.1974269389498738</v>
+        <v>0.3670268667978119</v>
       </c>
       <c r="K10">
-        <v>0.541</v>
+        <v>0.599</v>
       </c>
       <c r="L10">
-        <v>0.1762214983713355</v>
+        <v>0.3482558139534884</v>
       </c>
       <c r="M10">
-        <v>0.471</v>
+        <v>0.14</v>
       </c>
       <c r="N10">
-        <v>0.03738095238095238</v>
+        <v>0.009655172413793104</v>
       </c>
       <c r="O10">
-        <v>0.8706099815157116</v>
+        <v>0.2337228714524207</v>
       </c>
       <c r="P10">
-        <v>0.471</v>
+        <v>0.14</v>
       </c>
       <c r="Q10">
-        <v>0.03738095238095238</v>
+        <v>0.009655172413793104</v>
       </c>
       <c r="R10">
-        <v>0.8706099815157116</v>
+        <v>0.2337228714524207</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1561,16 +1585,22 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>0.5317241379310345</v>
+      </c>
+      <c r="W10">
+        <v>0.07779220779220779</v>
       </c>
       <c r="X10">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
+      </c>
+      <c r="Y10">
+        <v>-0.03485583905141496</v>
       </c>
       <c r="AB10">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -1582,31 +1612,37 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>-7.71</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>-1.135493372606775</v>
+      </c>
+      <c r="AK10">
+        <v>17.13333333333333</v>
       </c>
       <c r="AL10">
-        <v>0.08</v>
+        <v>0.045</v>
       </c>
       <c r="AM10">
-        <v>0.08</v>
+        <v>0.045</v>
       </c>
       <c r="AN10">
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>11.9375</v>
+        <v>20.17777777777778</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>-8.371335504885993</v>
       </c>
       <c r="AQ10">
-        <v>11.9375</v>
+        <v>20.17777777777778</v>
       </c>
     </row>
     <row r="11">
@@ -1617,7 +1653,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Asia Pacific General Insurance Company Limited (DSE:ASIAPACINS)</t>
+          <t>Standard Insurance Limited (DSE:STANDARINS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1626,46 +1662,46 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0677</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="E11">
-        <v>0.102</v>
+        <v>0.0571</v>
       </c>
       <c r="G11">
-        <v>0.4711111111111111</v>
+        <v>0.3948051948051948</v>
       </c>
       <c r="H11">
-        <v>0.4711111111111111</v>
+        <v>0.3948051948051948</v>
       </c>
       <c r="I11">
-        <v>0.3866666666666667</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="J11">
-        <v>0.221271676300578</v>
+        <v>0.2378321678321678</v>
       </c>
       <c r="K11">
-        <v>0.989</v>
+        <v>0.899</v>
       </c>
       <c r="L11">
-        <v>0.2197777777777778</v>
+        <v>0.2335064935064935</v>
       </c>
       <c r="M11">
-        <v>0.759</v>
+        <v>0.506</v>
       </c>
       <c r="N11">
-        <v>0.0443859649122807</v>
+        <v>0.02229074889867842</v>
       </c>
       <c r="O11">
-        <v>0.7674418604651163</v>
+        <v>0.5628476084538376</v>
       </c>
       <c r="P11">
-        <v>0.759</v>
+        <v>0.506</v>
       </c>
       <c r="Q11">
-        <v>0.0443859649122807</v>
+        <v>0.02229074889867842</v>
       </c>
       <c r="R11">
-        <v>0.7674418604651163</v>
+        <v>0.5628476084538376</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1674,67 +1710,64 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>9.529999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="V11">
-        <v>0.5573099415204678</v>
+        <v>0.4493392070484581</v>
       </c>
       <c r="W11">
-        <v>0.08990909090909091</v>
+        <v>0.1019274376417234</v>
       </c>
       <c r="X11">
-        <v>0.1227734454066811</v>
+        <v>0.1129167626440317</v>
       </c>
       <c r="Y11">
-        <v>-0.03286435449759016</v>
-      </c>
-      <c r="Z11">
-        <v>22.50000000000008</v>
-      </c>
-      <c r="AA11">
-        <v>4.978612716763023</v>
+        <v>-0.01098932500230834</v>
       </c>
       <c r="AB11">
-        <v>0.1227734454066811</v>
-      </c>
-      <c r="AC11">
-        <v>4.855839271356342</v>
+        <v>0.1126734095665353</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="AG11">
-        <v>-9.529999999999999</v>
+        <v>-10.082</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.00517135594705934</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.01377217553688142</v>
       </c>
       <c r="AJ11">
-        <v>-1.25891677675033</v>
+        <v>-0.7990172769060072</v>
       </c>
       <c r="AK11">
-        <v>-953.0000000000202</v>
+        <v>6.177696078431373</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>0.08027210884353742</v>
+      </c>
+      <c r="AO11">
+        <v>57.82608695652174</v>
       </c>
       <c r="AP11">
-        <v>-5.207650273224044</v>
+        <v>-6.858503401360544</v>
+      </c>
+      <c r="AQ11">
+        <v>57.82608695652174</v>
       </c>
     </row>
     <row r="12">
@@ -1745,7 +1778,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Global Insurance Limited (DSE:GLOBALINS)</t>
+          <t>Mercantile Islami Insurance PLC (DSE:MERCINS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1753,44 +1786,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.495</v>
-      </c>
       <c r="G12">
-        <v>0.1995987963891675</v>
+        <v>0.2652068126520681</v>
       </c>
       <c r="H12">
-        <v>0.1995987963891675</v>
+        <v>0.2652068126520681</v>
       </c>
       <c r="I12">
-        <v>0.09287863590772316</v>
+        <v>0.197323600973236</v>
       </c>
       <c r="J12">
-        <v>0.07098416838605145</v>
+        <v>0.197323600973236</v>
       </c>
       <c r="K12">
-        <v>0.616</v>
+        <v>0.79</v>
       </c>
       <c r="L12">
-        <v>0.06178535606820461</v>
+        <v>0.1922141119221411</v>
       </c>
       <c r="M12">
-        <v>0.499</v>
+        <v>0.392</v>
       </c>
       <c r="N12">
-        <v>0.04056910569105691</v>
+        <v>0.02903703703703704</v>
       </c>
       <c r="O12">
-        <v>0.810064935064935</v>
+        <v>0.4962025316455696</v>
       </c>
       <c r="P12">
-        <v>0.499</v>
+        <v>0.392</v>
       </c>
       <c r="Q12">
-        <v>0.04056910569105691</v>
+        <v>0.02903703703703704</v>
       </c>
       <c r="R12">
-        <v>0.810064935064935</v>
+        <v>0.4962025316455696</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1799,73 +1829,58 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>6.85</v>
+        <v>10.7</v>
       </c>
       <c r="V12">
-        <v>0.556910569105691</v>
+        <v>0.7925925925925925</v>
       </c>
       <c r="W12">
-        <v>0.09263157894736841</v>
+        <v>0.08936651583710407</v>
       </c>
       <c r="X12">
-        <v>0.1228563947856803</v>
+        <v>0.1129926710622263</v>
       </c>
       <c r="Y12">
-        <v>-0.03022481583831192</v>
-      </c>
-      <c r="Z12">
-        <v>51.65803108808301</v>
-      </c>
-      <c r="AA12">
-        <v>3.666902377248365</v>
+        <v>-0.02362615522512224</v>
       </c>
       <c r="AB12">
-        <v>0.1227782705935385</v>
-      </c>
-      <c r="AC12">
-        <v>3.544124106654826</v>
+        <v>0.1127198426238124</v>
       </c>
       <c r="AD12">
-        <v>0.018</v>
+        <v>0.09</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.018</v>
+        <v>0.09</v>
       </c>
       <c r="AG12">
-        <v>-6.832</v>
+        <v>-10.61</v>
       </c>
       <c r="AH12">
-        <v>0.001461276181198246</v>
+        <v>0.006622516556291391</v>
       </c>
       <c r="AI12">
-        <v>0.003328402366863905</v>
+        <v>0.0108695652173913</v>
       </c>
       <c r="AJ12">
-        <v>-1.249451353328456</v>
+        <v>-3.671280276816608</v>
       </c>
       <c r="AK12">
-        <v>4.737864077669903</v>
+        <v>4.384297520661157</v>
       </c>
       <c r="AL12">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>0.0174757281553398</v>
-      </c>
-      <c r="AO12">
-        <v>54.47058823529412</v>
+        <v>0.1032110091743119</v>
       </c>
       <c r="AP12">
-        <v>-6.633009708737863</v>
-      </c>
-      <c r="AQ12">
-        <v>54.47058823529412</v>
+        <v>-12.16743119266055</v>
       </c>
     </row>
     <row r="13">
@@ -1876,7 +1891,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Express Insurance Limited (DSE:EIL)</t>
+          <t>Asia Pacific General Insurance Company Limited (DSE:ASIAPACINS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1884,41 +1899,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.0132</v>
+      </c>
+      <c r="E13">
+        <v>0.0173</v>
+      </c>
       <c r="G13">
-        <v>0.8798076923076923</v>
+        <v>0.3481308411214953</v>
       </c>
       <c r="H13">
-        <v>0.8798076923076923</v>
+        <v>0.3481308411214953</v>
       </c>
       <c r="I13">
-        <v>0.764423076923077</v>
+        <v>0.3364485981308411</v>
       </c>
       <c r="J13">
-        <v>0.5525949953660797</v>
+        <v>0.2296320501927978</v>
       </c>
       <c r="K13">
-        <v>0.66</v>
+        <v>0.972</v>
       </c>
       <c r="L13">
-        <v>0.3173076923076923</v>
+        <v>0.2271028037383177</v>
       </c>
       <c r="M13">
-        <v>0.134</v>
+        <v>0.733</v>
       </c>
       <c r="N13">
-        <v>0.007745664739884394</v>
+        <v>0.03665</v>
       </c>
       <c r="O13">
-        <v>0.203030303030303</v>
+        <v>0.7541152263374485</v>
       </c>
       <c r="P13">
-        <v>0.134</v>
+        <v>0.733</v>
       </c>
       <c r="Q13">
-        <v>0.007745664739884394</v>
+        <v>0.03665</v>
       </c>
       <c r="R13">
-        <v>0.203030303030303</v>
+        <v>0.7541152263374485</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1927,31 +1948,31 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>12.7</v>
+        <v>8.33</v>
       </c>
       <c r="V13">
-        <v>0.7341040462427745</v>
+        <v>0.4165</v>
       </c>
       <c r="W13">
-        <v>0.05238095238095238</v>
+        <v>0.08836363636363637</v>
       </c>
       <c r="X13">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y13">
-        <v>-0.0703924930257287</v>
+        <v>-0.02428441047998638</v>
       </c>
       <c r="Z13">
-        <v>2.31111111111111</v>
+        <v>5.349999999999995</v>
       </c>
       <c r="AA13">
-        <v>1.277108433734939</v>
+        <v>1.228531468531467</v>
       </c>
       <c r="AB13">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC13">
-        <v>1.154334988328258</v>
+        <v>1.115883421687844</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -1963,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-12.7</v>
+        <v>-8.33</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -1972,28 +1993,22 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-2.76086956521739</v>
+        <v>-0.713796058269066</v>
       </c>
       <c r="AK13">
-        <v>127.0000000000004</v>
+        <v>-8.956989247311832</v>
       </c>
       <c r="AL13">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AN13">
         <v>0</v>
       </c>
-      <c r="AO13">
-        <v>79.5</v>
-      </c>
       <c r="AP13">
-        <v>-7.341040462427745</v>
-      </c>
-      <c r="AQ13">
-        <v>79.5</v>
+        <v>-5.590604026845638</v>
       </c>
     </row>
     <row r="14">
@@ -2004,7 +2019,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Takaful Islami Insurance Limited (DSE:TAKAFULINS)</t>
+          <t>Provati Insurance Company Limited (DSE:PROVATIINS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2013,46 +2028,43 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E14">
-        <v>0.0133</v>
+        <v>0.192</v>
       </c>
       <c r="G14">
-        <v>0.3036750483558994</v>
+        <v>0.1547861507128309</v>
       </c>
       <c r="H14">
-        <v>0.3036750483558994</v>
+        <v>0.1547861507128309</v>
       </c>
       <c r="I14">
-        <v>0.1895551257253385</v>
+        <v>0.1456211812627291</v>
       </c>
       <c r="J14">
-        <v>0.1453189242625087</v>
+        <v>0.1076592457335487</v>
       </c>
       <c r="K14">
-        <v>0.726</v>
+        <v>1.07</v>
       </c>
       <c r="L14">
-        <v>0.1404255319148936</v>
+        <v>0.1089613034623218</v>
       </c>
       <c r="M14">
-        <v>0.465</v>
+        <v>0.445</v>
       </c>
       <c r="N14">
-        <v>0.02473404255319149</v>
+        <v>0.02060185185185185</v>
       </c>
       <c r="O14">
-        <v>0.6404958677685951</v>
+        <v>0.4158878504672897</v>
       </c>
       <c r="P14">
-        <v>0.465</v>
+        <v>0.445</v>
       </c>
       <c r="Q14">
-        <v>0.02473404255319149</v>
+        <v>0.02060185185185185</v>
       </c>
       <c r="R14">
-        <v>0.6404958677685951</v>
+        <v>0.4158878504672897</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2061,55 +2073,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>6.7</v>
+        <v>7.02</v>
       </c>
       <c r="V14">
-        <v>0.3563829787234042</v>
+        <v>0.325</v>
       </c>
       <c r="W14">
-        <v>0.07682539682539682</v>
+        <v>0.1371794871794872</v>
       </c>
       <c r="X14">
-        <v>0.1227734454066811</v>
+        <v>0.1135407192987556</v>
       </c>
       <c r="Y14">
-        <v>-0.04594804858128425</v>
+        <v>0.02363876788073159</v>
       </c>
       <c r="Z14">
-        <v>8.338709677419365</v>
+        <v>10.35864978902954</v>
       </c>
       <c r="AA14">
-        <v>1.211772320059953</v>
+        <v>1.115204423104904</v>
       </c>
       <c r="AB14">
-        <v>0.1227734454066811</v>
+        <v>0.1128320796897349</v>
       </c>
       <c r="AC14">
-        <v>1.088998874653272</v>
+        <v>1.002372343415169</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="AG14">
-        <v>-6.7</v>
+        <v>-6.646999999999999</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.01697537887407272</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.04713762163528371</v>
       </c>
       <c r="AJ14">
-        <v>-0.5537190082644627</v>
+        <v>-0.4445261820370493</v>
       </c>
       <c r="AK14">
-        <v>-5.583333333333333</v>
+        <v>-7.443449048152289</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2118,10 +2130,10 @@
         <v>0</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>0.2274390243902439</v>
       </c>
       <c r="AP14">
-        <v>-6.38095238095238</v>
+        <v>-4.053048780487805</v>
       </c>
     </row>
     <row r="15">
@@ -2141,46 +2153,46 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.138</v>
+        <v>0.116</v>
       </c>
       <c r="E15">
-        <v>0.131</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G15">
-        <v>0.3723849372384937</v>
+        <v>0.2595936794582393</v>
       </c>
       <c r="H15">
-        <v>0.3723849372384937</v>
+        <v>0.2595936794582393</v>
       </c>
       <c r="I15">
-        <v>0.2970711297071129</v>
+        <v>0.1986455981941309</v>
       </c>
       <c r="J15">
-        <v>0.2186192468619247</v>
+        <v>0.1540288103378871</v>
       </c>
       <c r="K15">
-        <v>1.04</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L15">
-        <v>0.2175732217573222</v>
+        <v>0.1553047404063205</v>
       </c>
       <c r="M15">
-        <v>0.535</v>
+        <v>0.408</v>
       </c>
       <c r="N15">
-        <v>0.04458333333333334</v>
+        <v>0.02598726114649682</v>
       </c>
       <c r="O15">
-        <v>0.514423076923077</v>
+        <v>0.5930232558139535</v>
       </c>
       <c r="P15">
-        <v>0.535</v>
+        <v>0.408</v>
       </c>
       <c r="Q15">
-        <v>0.04458333333333334</v>
+        <v>0.02598726114649682</v>
       </c>
       <c r="R15">
-        <v>0.514423076923077</v>
+        <v>0.5930232558139535</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2189,31 +2201,31 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>7.98</v>
+        <v>6.97</v>
       </c>
       <c r="V15">
-        <v>0.665</v>
+        <v>0.4439490445859873</v>
       </c>
       <c r="W15">
-        <v>0.1009708737864078</v>
+        <v>0.07494553376906318</v>
       </c>
       <c r="X15">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y15">
-        <v>-0.02180257162027331</v>
+        <v>-0.03770251307455956</v>
       </c>
       <c r="Z15">
-        <v>3.229729729729729</v>
+        <v>3.691666666666669</v>
       </c>
       <c r="AA15">
-        <v>0.7060810810810808</v>
+        <v>0.5686230248307002</v>
       </c>
       <c r="AB15">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC15">
-        <v>0.5833076356743997</v>
+        <v>0.4559749779870774</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2225,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>-7.98</v>
+        <v>-6.97</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -2234,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>-1.985074626865672</v>
+        <v>-0.7983963344788086</v>
       </c>
       <c r="AK15">
-        <v>-6.650000000000004</v>
+        <v>-4.198795180722889</v>
       </c>
       <c r="AL15">
         <v>0.002</v>
@@ -2249,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>710</v>
+        <v>440</v>
       </c>
       <c r="AP15">
-        <v>-5.32</v>
+        <v>-7.298429319371728</v>
       </c>
       <c r="AQ15">
-        <v>710</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16">
@@ -2266,7 +2278,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prime Insurance Company Limited (DSE:PRIMEINSUR)</t>
+          <t>Takaful Islami Insurance Limited (DSE:TAKAFULINS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2275,46 +2287,46 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.177</v>
+        <v>0.0863</v>
       </c>
       <c r="E16">
-        <v>0.0633</v>
+        <v>-0.0131</v>
       </c>
       <c r="G16">
-        <v>0.1507479861910242</v>
+        <v>0.2046709129511677</v>
       </c>
       <c r="H16">
-        <v>0.1507479861910242</v>
+        <v>0.2046709129511677</v>
       </c>
       <c r="I16">
-        <v>0.1760644418872267</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="J16">
-        <v>0.1279090680465481</v>
+        <v>0.1204188481675393</v>
       </c>
       <c r="K16">
-        <v>1.1</v>
+        <v>0.552</v>
       </c>
       <c r="L16">
-        <v>0.1265822784810127</v>
+        <v>0.1171974522292994</v>
       </c>
       <c r="M16">
-        <v>0.575</v>
+        <v>0.464</v>
       </c>
       <c r="N16">
-        <v>0.01747720364741641</v>
+        <v>0.02846625766871166</v>
       </c>
       <c r="O16">
-        <v>0.5227272727272726</v>
+        <v>0.8405797101449275</v>
       </c>
       <c r="P16">
-        <v>0.575</v>
+        <v>0.464</v>
       </c>
       <c r="Q16">
-        <v>0.01747720364741641</v>
+        <v>0.02846625766871166</v>
       </c>
       <c r="R16">
-        <v>0.5227272727272726</v>
+        <v>0.8405797101449275</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2323,31 +2335,31 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>6.18</v>
+        <v>6.62</v>
       </c>
       <c r="V16">
-        <v>0.1878419452887538</v>
+        <v>0.4061349693251534</v>
       </c>
       <c r="W16">
-        <v>0.1224944320712695</v>
+        <v>0.06987341772151899</v>
       </c>
       <c r="X16">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y16">
-        <v>-0.000279013335411582</v>
+        <v>-0.04277462912210375</v>
       </c>
       <c r="Z16">
-        <v>2.976027397260273</v>
+        <v>3.924999999999999</v>
       </c>
       <c r="AA16">
-        <v>0.3806608908645558</v>
+        <v>0.4726439790575916</v>
       </c>
       <c r="AB16">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC16">
-        <v>0.2578874454578748</v>
+        <v>0.3599959322139689</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2359,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>-6.18</v>
+        <v>-6.62</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2368,10 +2380,10 @@
         <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.2312874251497006</v>
+        <v>-0.6838842975206612</v>
       </c>
       <c r="AK16">
-        <v>-3.304812834224597</v>
+        <v>-9.735294117647063</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2383,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>-3.395604395604396</v>
+        <v>-7.843601895734597</v>
       </c>
     </row>
     <row r="17">
@@ -2394,7 +2406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Janata Insurance Company Limited (DSE:JANATAINS)</t>
+          <t>Meghna Insurance Company Limited (DSE:MEGHNAINS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2402,47 +2414,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.0771</v>
-      </c>
-      <c r="E17">
-        <v>0.235</v>
-      </c>
       <c r="G17">
-        <v>0.2952127659574468</v>
+        <v>0.2281553398058252</v>
       </c>
       <c r="H17">
-        <v>0.2952127659574468</v>
+        <v>0.2281553398058252</v>
       </c>
       <c r="I17">
-        <v>0.2372340425531915</v>
+        <v>0.2512135922330097</v>
       </c>
       <c r="J17">
-        <v>0.1523262580008602</v>
+        <v>0.1972974674848873</v>
       </c>
       <c r="K17">
-        <v>0.54</v>
+        <v>1.66</v>
       </c>
       <c r="L17">
-        <v>0.1436170212765958</v>
+        <v>0.2014563106796116</v>
       </c>
       <c r="M17">
-        <v>0.323</v>
+        <v>0.112</v>
       </c>
       <c r="N17">
-        <v>0.02484615384615385</v>
+        <v>0.008</v>
       </c>
       <c r="O17">
-        <v>0.5981481481481481</v>
+        <v>0.06746987951807229</v>
       </c>
       <c r="P17">
-        <v>0.323</v>
+        <v>0.112</v>
       </c>
       <c r="Q17">
-        <v>0.02484615384615385</v>
+        <v>0.008</v>
       </c>
       <c r="R17">
-        <v>0.5981481481481481</v>
+        <v>0.06746987951807229</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2451,73 +2457,73 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>5.24</v>
+        <v>0.619</v>
       </c>
       <c r="V17">
-        <v>0.4030769230769231</v>
+        <v>0.04421428571428571</v>
       </c>
       <c r="W17">
-        <v>0.07161803713527852</v>
+        <v>0.7155172413793104</v>
       </c>
       <c r="X17">
-        <v>0.1227734454066811</v>
+        <v>0.1130357490895518</v>
       </c>
       <c r="Y17">
-        <v>-0.05115540827140255</v>
+        <v>0.6024814922897587</v>
       </c>
       <c r="Z17">
-        <v>1.928205128205128</v>
+        <v>2.361031518624642</v>
       </c>
       <c r="AA17">
-        <v>0.2937162718375559</v>
+        <v>0.4658255392766394</v>
       </c>
       <c r="AB17">
-        <v>0.1227734454066811</v>
+        <v>0.1127287502888483</v>
       </c>
       <c r="AC17">
-        <v>0.1709428264308749</v>
+        <v>0.3530967889877911</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AG17">
-        <v>-5.24</v>
+        <v>-0.514</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>0.007444168734491314</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>0.019644527595884</v>
       </c>
       <c r="AJ17">
-        <v>-0.6752577319587629</v>
+        <v>-0.03811359928815067</v>
       </c>
       <c r="AK17">
-        <v>-3.881481481481483</v>
+        <v>-0.1087600507829031</v>
       </c>
       <c r="AL17">
-        <v>0.031</v>
+        <v>0.007</v>
       </c>
       <c r="AM17">
-        <v>0.031</v>
+        <v>0.007</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>0.04411764705882353</v>
       </c>
       <c r="AO17">
-        <v>28.7741935483871</v>
+        <v>295.7142857142857</v>
       </c>
       <c r="AP17">
-        <v>-5.521601685985248</v>
+        <v>-0.2159663865546219</v>
       </c>
       <c r="AQ17">
-        <v>28.7741935483871</v>
+        <v>295.7142857142857</v>
       </c>
     </row>
     <row r="18">
@@ -2528,7 +2534,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eastern Insurance Company Limited (DSE:EASTERNINS)</t>
+          <t>Janata Insurance Company Limited (DSE:JANATAINS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2536,41 +2542,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.113</v>
+      </c>
+      <c r="E18">
+        <v>0.223</v>
+      </c>
       <c r="G18">
-        <v>0.7888631090487239</v>
+        <v>0.2313775510204082</v>
       </c>
       <c r="H18">
-        <v>0.7888631090487239</v>
+        <v>0.2313775510204082</v>
       </c>
       <c r="I18">
-        <v>0.4895591647331787</v>
+        <v>0.2216836734693877</v>
       </c>
       <c r="J18">
-        <v>0.4047647065353746</v>
+        <v>0.1466642570377097</v>
       </c>
       <c r="K18">
-        <v>1.73</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L18">
-        <v>0.4013921113689096</v>
+        <v>0.1441326530612245</v>
       </c>
       <c r="M18">
-        <v>0.79</v>
+        <v>0.33</v>
       </c>
       <c r="N18">
-        <v>0.0383495145631068</v>
+        <v>0.02244897959183674</v>
       </c>
       <c r="O18">
-        <v>0.4566473988439307</v>
+        <v>0.5840707964601771</v>
       </c>
       <c r="P18">
-        <v>0.79</v>
+        <v>0.33</v>
       </c>
       <c r="Q18">
-        <v>0.0383495145631068</v>
+        <v>0.02244897959183674</v>
       </c>
       <c r="R18">
-        <v>0.4566473988439307</v>
+        <v>0.5840707964601771</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2579,31 +2591,31 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>14.9</v>
+        <v>5.32</v>
       </c>
       <c r="V18">
-        <v>0.7233009708737864</v>
+        <v>0.361904761904762</v>
       </c>
       <c r="W18">
-        <v>0.07972350230414747</v>
+        <v>0.0857359635811836</v>
       </c>
       <c r="X18">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y18">
-        <v>-0.0430499431025336</v>
+        <v>-0.02691208326243914</v>
       </c>
       <c r="Z18">
-        <v>0.6951612903225807</v>
+        <v>2.903703703703704</v>
       </c>
       <c r="AA18">
-        <v>0.2813767556721716</v>
+        <v>0.4258695463613497</v>
       </c>
       <c r="AB18">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC18">
-        <v>0.1586033102654906</v>
+        <v>0.313221499517727</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -2615,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>-14.9</v>
+        <v>-5.32</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -2624,28 +2636,22 @@
         <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-2.614035087719298</v>
+        <v>-0.5671641791044777</v>
       </c>
       <c r="AK18">
-        <v>-2.403225806451613</v>
+        <v>-5.720430107526884</v>
       </c>
       <c r="AL18">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AN18">
         <v>0</v>
       </c>
-      <c r="AO18">
-        <v>263.75</v>
-      </c>
       <c r="AP18">
-        <v>-6.898148148148148</v>
-      </c>
-      <c r="AQ18">
-        <v>263.75</v>
+        <v>-5.605900948366703</v>
       </c>
     </row>
     <row r="19">
@@ -2656,7 +2662,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pioneer Insurance Company Limited (DSE:PIONEERINS)</t>
+          <t>Prime Insurance Company Limited (DSE:PRIMEINSUR)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2665,46 +2671,46 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0367</v>
+        <v>0.191</v>
       </c>
       <c r="E19">
-        <v>0.253</v>
+        <v>0.101</v>
       </c>
       <c r="G19">
-        <v>0.523076923076923</v>
+        <v>0.2552594670406732</v>
       </c>
       <c r="H19">
-        <v>0.523076923076923</v>
+        <v>0.2552594670406732</v>
       </c>
       <c r="I19">
-        <v>0.4353846153846154</v>
+        <v>0.150070126227209</v>
       </c>
       <c r="J19">
-        <v>0.3064776365133083</v>
+        <v>0.1105324198942712</v>
       </c>
       <c r="K19">
-        <v>5.93</v>
+        <v>0.763</v>
       </c>
       <c r="L19">
-        <v>0.3041025641025641</v>
+        <v>0.1070126227208976</v>
       </c>
       <c r="M19">
-        <v>1.5</v>
+        <v>0.018</v>
       </c>
       <c r="N19">
-        <v>0.02546689303904924</v>
+        <v>0.0005825242718446601</v>
       </c>
       <c r="O19">
-        <v>0.2529510961214165</v>
+        <v>0.0235910878112713</v>
       </c>
       <c r="P19">
-        <v>1.5</v>
+        <v>0.018</v>
       </c>
       <c r="Q19">
-        <v>0.02546689303904924</v>
+        <v>0.0005825242718446601</v>
       </c>
       <c r="R19">
-        <v>0.2529510961214165</v>
+        <v>0.0235910878112713</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2713,31 +2719,31 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>22.6</v>
+        <v>5.72</v>
       </c>
       <c r="V19">
-        <v>0.3837011884550085</v>
+        <v>0.1851132686084142</v>
       </c>
       <c r="W19">
-        <v>0.1323660714285714</v>
+        <v>0.09478260869565217</v>
       </c>
       <c r="X19">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y19">
-        <v>0.009592626021890358</v>
+        <v>-0.01786543814797058</v>
       </c>
       <c r="Z19">
-        <v>0.8024691358024693</v>
+        <v>3.812834224598928</v>
       </c>
       <c r="AA19">
-        <v>0.2459388441156178</v>
+        <v>0.4214417935006168</v>
       </c>
       <c r="AB19">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC19">
-        <v>0.1231653987089368</v>
+        <v>0.3087937466569941</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -2749,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>-22.6</v>
+        <v>-5.72</v>
       </c>
       <c r="AH19">
         <v>0</v>
@@ -2758,10 +2764,10 @@
         <v>0</v>
       </c>
       <c r="AJ19">
-        <v>-0.6225895316804408</v>
+        <v>-0.227164416203336</v>
       </c>
       <c r="AK19">
-        <v>-1.076190476190476</v>
+        <v>-2.363636363636363</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2773,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>-2.603686635944701</v>
+        <v>-3.788079470198675</v>
       </c>
     </row>
     <row r="20">
@@ -2784,7 +2790,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Central Insurance Company Limited (DSE:CENTRALINS)</t>
+          <t>Union Insurance Co. Ltd. (DSE:UNIONINS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2792,47 +2798,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.0766</v>
-      </c>
-      <c r="E20">
-        <v>0.142</v>
-      </c>
       <c r="G20">
-        <v>0.5458422174840085</v>
+        <v>0.2863849765258216</v>
       </c>
       <c r="H20">
-        <v>0.5458422174840085</v>
+        <v>0.2863849765258216</v>
       </c>
       <c r="I20">
-        <v>0.4093816631130063</v>
+        <v>0.3317683881064163</v>
       </c>
       <c r="J20">
-        <v>0.3454157782515991</v>
+        <v>0.3085446009389672</v>
       </c>
       <c r="K20">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="L20">
-        <v>0.3454157782515991</v>
+        <v>0.3051643192488263</v>
       </c>
       <c r="M20">
-        <v>0.912</v>
+        <v>0.17</v>
       </c>
       <c r="N20">
-        <v>0.0492972972972973</v>
+        <v>0.006390977443609023</v>
       </c>
       <c r="O20">
-        <v>0.562962962962963</v>
+        <v>0.08717948717948719</v>
       </c>
       <c r="P20">
-        <v>0.912</v>
+        <v>0.17</v>
       </c>
       <c r="Q20">
-        <v>0.0492972972972973</v>
+        <v>0.006390977443609023</v>
       </c>
       <c r="R20">
-        <v>0.562962962962963</v>
+        <v>0.08717948717948719</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2841,31 +2841,31 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>7.67</v>
+        <v>1.56</v>
       </c>
       <c r="V20">
-        <v>0.4145945945945946</v>
+        <v>0.05864661654135338</v>
       </c>
       <c r="W20">
-        <v>0.1045161290322581</v>
+        <v>0.2296819787985866</v>
       </c>
       <c r="X20">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y20">
-        <v>-0.018257316374423</v>
+        <v>0.1170339319549638</v>
       </c>
       <c r="Z20">
-        <v>0.6937869822485208</v>
+        <v>1.091374893253629</v>
       </c>
       <c r="AA20">
-        <v>0.2396449704142012</v>
+        <v>0.3367378309137489</v>
       </c>
       <c r="AB20">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC20">
-        <v>0.1168715250075201</v>
+        <v>0.2240897840701262</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>-7.67</v>
+        <v>-1.56</v>
       </c>
       <c r="AH20">
         <v>0</v>
@@ -2886,22 +2886,28 @@
         <v>0</v>
       </c>
       <c r="AJ20">
-        <v>-0.7082179132040628</v>
+        <v>-0.06230031948881789</v>
       </c>
       <c r="AK20">
-        <v>-0.4161692892023874</v>
+        <v>-0.223816355810617</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AN20">
         <v>0</v>
       </c>
+      <c r="AO20">
+        <v>424</v>
+      </c>
       <c r="AP20">
-        <v>-3.567441860465117</v>
+        <v>-0.7222222222222222</v>
+      </c>
+      <c r="AQ20">
+        <v>424</v>
       </c>
     </row>
     <row r="21">
@@ -2921,46 +2927,46 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.259</v>
+        <v>0.11</v>
       </c>
       <c r="E21">
-        <v>0.0352</v>
+        <v>-0.0722</v>
       </c>
       <c r="G21">
-        <v>0.1321160042964554</v>
+        <v>0.2015355086372361</v>
       </c>
       <c r="H21">
-        <v>0.1321160042964554</v>
+        <v>0.2015355086372361</v>
       </c>
       <c r="I21">
-        <v>0.112781954887218</v>
+        <v>0.1138195777351248</v>
       </c>
       <c r="J21">
-        <v>0.08371891266628109</v>
+        <v>0.07071513032060106</v>
       </c>
       <c r="K21">
-        <v>0.772</v>
+        <v>0.356</v>
       </c>
       <c r="L21">
-        <v>0.08292158968850698</v>
+        <v>0.06833013435700576</v>
       </c>
       <c r="M21">
-        <v>0.442</v>
+        <v>0.361</v>
       </c>
       <c r="N21">
-        <v>0.02695121951219513</v>
+        <v>0.02051136363636363</v>
       </c>
       <c r="O21">
-        <v>0.572538860103627</v>
+        <v>1.014044943820225</v>
       </c>
       <c r="P21">
-        <v>0.442</v>
+        <v>0.361</v>
       </c>
       <c r="Q21">
-        <v>0.02695121951219513</v>
+        <v>0.02051136363636363</v>
       </c>
       <c r="R21">
-        <v>0.572538860103627</v>
+        <v>1.014044943820225</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2969,31 +2975,31 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>7.65</v>
+        <v>8.06</v>
       </c>
       <c r="V21">
-        <v>0.4664634146341464</v>
+        <v>0.4579545454545454</v>
       </c>
       <c r="W21">
-        <v>0.07423076923076923</v>
+        <v>0.03907793633369924</v>
       </c>
       <c r="X21">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y21">
-        <v>-0.04854267617591185</v>
+        <v>-0.07357011050992351</v>
       </c>
       <c r="Z21">
-        <v>2.714285714285714</v>
+        <v>3.568493150684934</v>
       </c>
       <c r="AA21">
-        <v>0.2272370486656201</v>
+        <v>0.2523464581988574</v>
       </c>
       <c r="AB21">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC21">
-        <v>0.104463603258939</v>
+        <v>0.1396984113552346</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -3005,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>-7.65</v>
+        <v>-8.06</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -3014,10 +3020,10 @@
         <v>0</v>
       </c>
       <c r="AJ21">
-        <v>-0.8742857142857146</v>
+        <v>-0.8448637316561844</v>
       </c>
       <c r="AK21">
-        <v>-5.239726027397264</v>
+        <v>-7.196428571428577</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3029,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>-6.428571428571429</v>
+        <v>-10.59132720105125</v>
       </c>
     </row>
     <row r="22">
@@ -3040,7 +3046,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>City General Insurance Company Limited (DSE:CITYGENINS)</t>
+          <t>Pioneer Insurance Company Limited (DSE:PIONEERINS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3049,46 +3055,46 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.145</v>
+        <v>0.0234</v>
       </c>
       <c r="E22">
-        <v>0.0315</v>
+        <v>0.115</v>
       </c>
       <c r="G22">
-        <v>0.2509270704573547</v>
+        <v>0.4101123595505617</v>
       </c>
       <c r="H22">
-        <v>0.2509270704573547</v>
+        <v>0.4101123595505617</v>
       </c>
       <c r="I22">
-        <v>0.242274412855377</v>
+        <v>0.351685393258427</v>
       </c>
       <c r="J22">
-        <v>0.1716005815405701</v>
+        <v>0.2524193548387097</v>
       </c>
       <c r="K22">
-        <v>1.37</v>
+        <v>4.44</v>
       </c>
       <c r="L22">
-        <v>0.169344870210136</v>
+        <v>0.249438202247191</v>
       </c>
       <c r="M22">
-        <v>0.6820000000000001</v>
+        <v>1.92</v>
       </c>
       <c r="N22">
-        <v>0.03965116279069768</v>
+        <v>0.03453237410071942</v>
       </c>
       <c r="O22">
-        <v>0.4978102189781022</v>
+        <v>0.4324324324324324</v>
       </c>
       <c r="P22">
-        <v>0.6820000000000001</v>
+        <v>1.92</v>
       </c>
       <c r="Q22">
-        <v>0.03965116279069768</v>
+        <v>0.03453237410071942</v>
       </c>
       <c r="R22">
-        <v>0.4978102189781022</v>
+        <v>0.4324324324324324</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3097,31 +3103,31 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>7.64</v>
+        <v>13.4</v>
       </c>
       <c r="V22">
-        <v>0.4441860465116279</v>
+        <v>0.2410071942446043</v>
       </c>
       <c r="W22">
-        <v>0.09319727891156464</v>
+        <v>0.1138461538461539</v>
       </c>
       <c r="X22">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y22">
-        <v>-0.02957616649511643</v>
+        <v>0.001198107002531118</v>
       </c>
       <c r="Z22">
-        <v>1.187958883994126</v>
+        <v>0.9673913043478262</v>
       </c>
       <c r="AA22">
-        <v>0.2038544353396788</v>
+        <v>0.2441882889200561</v>
       </c>
       <c r="AB22">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC22">
-        <v>0.08108098993299771</v>
+        <v>0.1315402420764334</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -3133,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>-7.64</v>
+        <v>-13.4</v>
       </c>
       <c r="AH22">
         <v>0</v>
@@ -3142,28 +3148,22 @@
         <v>0</v>
       </c>
       <c r="AJ22">
-        <v>-0.799163179916318</v>
+        <v>-0.3175355450236967</v>
       </c>
       <c r="AK22">
-        <v>-1.425373134328358</v>
+        <v>-0.5537190082644627</v>
       </c>
       <c r="AL22">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AN22">
         <v>0</v>
       </c>
-      <c r="AO22">
-        <v>163.3333333333333</v>
-      </c>
       <c r="AP22">
-        <v>-3.745098039215686</v>
-      </c>
-      <c r="AQ22">
-        <v>163.3333333333333</v>
+        <v>-2.042682926829269</v>
       </c>
     </row>
     <row r="23">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Federal Insurance Company Limited (DSE:FEDERALINS)</t>
+          <t>Continental Insurance Limited (DSE:CONTININS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3183,46 +3183,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.144</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="E23">
-        <v>0.303</v>
+        <v>0.0291</v>
       </c>
       <c r="G23">
-        <v>0.3248175182481752</v>
+        <v>0.2669789227166277</v>
       </c>
       <c r="H23">
-        <v>0.3248175182481752</v>
+        <v>0.2669789227166277</v>
       </c>
       <c r="I23">
-        <v>0.2937956204379562</v>
+        <v>0.2320843091334895</v>
       </c>
       <c r="J23">
-        <v>0.2095980950685419</v>
+        <v>0.1797975147272198</v>
       </c>
       <c r="K23">
-        <v>1.17</v>
+        <v>0.729</v>
       </c>
       <c r="L23">
-        <v>0.2135036496350365</v>
+        <v>0.1707259953161593</v>
       </c>
       <c r="M23">
-        <v>0.369</v>
+        <v>0.33</v>
       </c>
       <c r="N23">
-        <v>0.02157894736842105</v>
+        <v>0.02101910828025478</v>
       </c>
       <c r="O23">
-        <v>0.3153846153846154</v>
+        <v>0.4526748971193416</v>
       </c>
       <c r="P23">
-        <v>0.369</v>
+        <v>0.33</v>
       </c>
       <c r="Q23">
-        <v>0.02157894736842105</v>
+        <v>0.02101910828025478</v>
       </c>
       <c r="R23">
-        <v>0.3153846153846154</v>
+        <v>0.4526748971193416</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3231,73 +3231,73 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="V23">
-        <v>0.2935672514619883</v>
+        <v>0.2980891719745223</v>
       </c>
       <c r="W23">
-        <v>0.1158415841584158</v>
+        <v>0.08398617511520737</v>
       </c>
       <c r="X23">
-        <v>0.1231181784983506</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y23">
-        <v>-0.007276594339934772</v>
+        <v>-0.02866187172841538</v>
       </c>
       <c r="Z23">
-        <v>0.9617409617409618</v>
+        <v>1.209631728045326</v>
       </c>
       <c r="AA23">
-        <v>0.201579073530293</v>
+        <v>0.2174887784377418</v>
       </c>
       <c r="AB23">
-        <v>0.1227934065648674</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC23">
-        <v>0.07878566696542563</v>
+        <v>0.1048407315941191</v>
       </c>
       <c r="AD23">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>-4.915999999999999</v>
+        <v>-4.68</v>
       </c>
       <c r="AH23">
-        <v>0.006045105789351313</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>0.01126272471301711</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>-0.4034799737360472</v>
+        <v>-0.4246823956442831</v>
       </c>
       <c r="AK23">
-        <v>-1.166587565258661</v>
+        <v>-1.275204359673024</v>
       </c>
       <c r="AL23">
-        <v>0.008999999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="AM23">
-        <v>0.008999999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="AN23">
-        <v>0.0608187134502924</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>178.8888888888889</v>
+        <v>16.24590163934426</v>
       </c>
       <c r="AP23">
-        <v>-2.874853801169591</v>
+        <v>-4.415094339622641</v>
       </c>
       <c r="AQ23">
-        <v>178.8888888888889</v>
+        <v>16.24590163934426</v>
       </c>
     </row>
     <row r="24">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Asia Insurance Limited (DSE:ASIAINS)</t>
+          <t>Islami Commercial Insurance Company Limited (DSE:ICICL)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3316,47 +3316,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.0823</v>
-      </c>
-      <c r="E24">
-        <v>0.161</v>
-      </c>
       <c r="G24">
-        <v>0.4494219653179191</v>
+        <v>0.266839378238342</v>
       </c>
       <c r="H24">
-        <v>0.4494219653179191</v>
+        <v>0.266839378238342</v>
       </c>
       <c r="I24">
-        <v>0.3294797687861272</v>
+        <v>0.2450777202072539</v>
       </c>
       <c r="J24">
-        <v>0.2779531970156095</v>
+        <v>0.1580252268304691</v>
       </c>
       <c r="K24">
-        <v>1.91</v>
+        <v>0.57</v>
       </c>
       <c r="L24">
-        <v>0.2760115606936416</v>
+        <v>0.1476683937823834</v>
       </c>
       <c r="M24">
-        <v>0.719</v>
+        <v>0.389</v>
       </c>
       <c r="N24">
-        <v>0.03209821428571429</v>
+        <v>0.02646258503401361</v>
       </c>
       <c r="O24">
-        <v>0.3764397905759163</v>
+        <v>0.6824561403508773</v>
       </c>
       <c r="P24">
-        <v>0.719</v>
+        <v>0.389</v>
       </c>
       <c r="Q24">
-        <v>0.03209821428571429</v>
+        <v>0.02646258503401361</v>
       </c>
       <c r="R24">
-        <v>0.3764397905759163</v>
+        <v>0.6824561403508773</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3365,73 +3359,67 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>1.7</v>
+        <v>4.47</v>
       </c>
       <c r="V24">
-        <v>0.07589285714285715</v>
+        <v>0.3040816326530612</v>
       </c>
       <c r="W24">
-        <v>0.1552845528455284</v>
+        <v>0.08456973293768545</v>
       </c>
       <c r="X24">
-        <v>0.1230998734316269</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y24">
-        <v>0.03218467941390153</v>
+        <v>-0.02807831390593729</v>
       </c>
       <c r="Z24">
-        <v>0.671909894164482</v>
+        <v>1.335640138408304</v>
       </c>
       <c r="AA24">
-        <v>0.1867595031894376</v>
+        <v>0.2110648358358514</v>
       </c>
       <c r="AB24">
-        <v>0.1227776656415158</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC24">
-        <v>0.0639818375479218</v>
+        <v>0.09841678899222871</v>
       </c>
       <c r="AD24">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>-1.571</v>
+        <v>-4.47</v>
       </c>
       <c r="AH24">
-        <v>0.00572595321585512</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>0.01128707673462245</v>
+        <v>0</v>
       </c>
       <c r="AJ24">
-        <v>-0.07542368812713045</v>
+        <v>-0.4369501466275659</v>
       </c>
       <c r="AK24">
-        <v>-0.161475999588858</v>
+        <v>-1.388198757763975</v>
       </c>
       <c r="AL24">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>0.05139442231075698</v>
-      </c>
-      <c r="AO24">
-        <v>87.69230769230769</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>-0.6258964143426295</v>
-      </c>
-      <c r="AQ24">
-        <v>87.69230769230769</v>
+        <v>-4.38235294117647</v>
       </c>
     </row>
     <row r="25">
@@ -3442,7 +3430,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Continental Insurance Limited (DSE:CONTININS)</t>
+          <t>Republic Insurance Company Limited (DSE:REPUBLIC)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3451,46 +3439,46 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.04</v>
+        <v>0.122</v>
       </c>
       <c r="E25">
-        <v>0.0253</v>
+        <v>0.195</v>
       </c>
       <c r="G25">
-        <v>0.2857142857142857</v>
+        <v>0.3306709265175719</v>
       </c>
       <c r="H25">
-        <v>0.2857142857142857</v>
+        <v>0.3306709265175719</v>
       </c>
       <c r="I25">
-        <v>0.2214285714285714</v>
+        <v>0.2955271565495208</v>
       </c>
       <c r="J25">
-        <v>0.1675801138065289</v>
+        <v>0.2057447214890957</v>
       </c>
       <c r="K25">
-        <v>0.722</v>
+        <v>1.28</v>
       </c>
       <c r="L25">
-        <v>0.1663594470046083</v>
+        <v>0.2044728434504793</v>
       </c>
       <c r="M25">
-        <v>0.421</v>
+        <v>0.453</v>
       </c>
       <c r="N25">
-        <v>0.03422764227642276</v>
+        <v>0.02199029126213592</v>
       </c>
       <c r="O25">
-        <v>0.5831024930747922</v>
+        <v>0.35390625</v>
       </c>
       <c r="P25">
-        <v>0.421</v>
+        <v>0.453</v>
       </c>
       <c r="Q25">
-        <v>0.03422764227642276</v>
+        <v>0.02199029126213592</v>
       </c>
       <c r="R25">
-        <v>0.5831024930747922</v>
+        <v>0.35390625</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3499,73 +3487,67 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>5.15</v>
+        <v>0.311</v>
       </c>
       <c r="V25">
-        <v>0.4186991869918699</v>
+        <v>0.01509708737864078</v>
       </c>
       <c r="W25">
-        <v>0.07148514851485148</v>
+        <v>0.1464530892448513</v>
       </c>
       <c r="X25">
-        <v>0.1227734454066811</v>
+        <v>0.1129366278033757</v>
       </c>
       <c r="Y25">
-        <v>-0.05128829689182959</v>
+        <v>0.03351646144147553</v>
       </c>
       <c r="Z25">
-        <v>0.9475982532751092</v>
+        <v>0.7694198623402164</v>
       </c>
       <c r="AA25">
-        <v>0.1587986231267108</v>
+        <v>0.1583040752853662</v>
       </c>
       <c r="AB25">
-        <v>0.1227734454066811</v>
+        <v>0.1127082319135234</v>
       </c>
       <c r="AC25">
-        <v>0.03602517772002971</v>
+        <v>0.04559584337184272</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AG25">
-        <v>-5.15</v>
+        <v>-0.196</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>0.005551532705768767</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>0.01341107871720116</v>
       </c>
       <c r="AJ25">
-        <v>-0.7202797202797203</v>
+        <v>-0.009605959615761616</v>
       </c>
       <c r="AK25">
-        <v>-1.458923512747876</v>
+        <v>-0.02371732817037754</v>
       </c>
       <c r="AL25">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>87.36363636363636</v>
+        <v>0.05989583333333334</v>
       </c>
       <c r="AP25">
-        <v>-5.049019607843137</v>
-      </c>
-      <c r="AQ25">
-        <v>87.36363636363636</v>
+        <v>-0.1020833333333333</v>
       </c>
     </row>
     <row r="26">
@@ -3576,7 +3558,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crystal Insurance Company Limited (DSE:CRYSTALINS)</t>
+          <t>Federal Insurance Company Limited (DSE:FEDERALINS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3584,41 +3566,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D26">
+        <v>0.0381</v>
+      </c>
+      <c r="E26">
+        <v>0.105</v>
+      </c>
       <c r="G26">
-        <v>1.009569377990431</v>
+        <v>0.3156565656565656</v>
       </c>
       <c r="H26">
-        <v>1.009569377990431</v>
+        <v>0.3156565656565656</v>
       </c>
       <c r="I26">
-        <v>0.7511961722488039</v>
+        <v>0.25</v>
       </c>
       <c r="J26">
-        <v>0.7511961722488039</v>
+        <v>0.1597151576805697</v>
       </c>
       <c r="K26">
-        <v>1.5</v>
+        <v>0.627</v>
       </c>
       <c r="L26">
-        <v>0.7177033492822967</v>
+        <v>0.1583333333333333</v>
       </c>
       <c r="M26">
-        <v>0.399</v>
+        <v>0.597</v>
       </c>
       <c r="N26">
-        <v>0.02541401273885351</v>
+        <v>0.03662576687116564</v>
       </c>
       <c r="O26">
-        <v>0.266</v>
+        <v>0.9521531100478469</v>
       </c>
       <c r="P26">
-        <v>0.399</v>
+        <v>0.597</v>
       </c>
       <c r="Q26">
-        <v>0.02541401273885351</v>
+        <v>0.03662576687116564</v>
       </c>
       <c r="R26">
-        <v>0.266</v>
+        <v>0.9521531100478469</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3627,73 +3615,73 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>0.379</v>
+        <v>3.9</v>
       </c>
       <c r="V26">
-        <v>0.02414012738853503</v>
+        <v>0.2392638036809816</v>
       </c>
       <c r="W26">
-        <v>0.1442307692307692</v>
+        <v>0.06867469879518072</v>
       </c>
       <c r="X26">
-        <v>0.1230406093301246</v>
+        <v>0.1128890723707443</v>
       </c>
       <c r="Y26">
-        <v>0.02119015990064461</v>
+        <v>-0.04421437357556354</v>
       </c>
       <c r="Z26">
-        <v>0.2085620197585071</v>
+        <v>0.9397247271001423</v>
       </c>
       <c r="AA26">
-        <v>0.1566709909190699</v>
+        <v>0.1500882829651295</v>
       </c>
       <c r="AB26">
-        <v>0.1227769030381793</v>
+        <v>0.1126983600076101</v>
       </c>
       <c r="AC26">
-        <v>0.03389408788089063</v>
+        <v>0.03738992295751949</v>
       </c>
       <c r="AD26">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="AG26">
-        <v>-0.305</v>
+        <v>-3.824</v>
       </c>
       <c r="AH26">
-        <v>0.004691264105490047</v>
+        <v>0.004640937957987298</v>
       </c>
       <c r="AI26">
-        <v>0.007794396460922687</v>
+        <v>0.009030418250950569</v>
       </c>
       <c r="AJ26">
-        <v>-0.01981162715167262</v>
+        <v>-0.3065084963129208</v>
       </c>
       <c r="AK26">
-        <v>-0.03346132748217224</v>
+        <v>-0.8467670504871567</v>
       </c>
       <c r="AL26">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="AM26">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="AN26">
-        <v>0.03814432989690721</v>
+        <v>0.06846846846846846</v>
       </c>
       <c r="AO26">
-        <v>142.7272727272727</v>
+        <v>141.4285714285714</v>
       </c>
       <c r="AP26">
-        <v>-0.1572164948453608</v>
+        <v>-3.445045045045044</v>
       </c>
       <c r="AQ26">
-        <v>142.7272727272727</v>
+        <v>141.4285714285714</v>
       </c>
     </row>
     <row r="27">
@@ -3704,7 +3692,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rupali Insurance Company Limited (DSE:RUPALIINS)</t>
+          <t>Eastern Insurance Company Limited (DSE:EASTERNINS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3712,47 +3700,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D27">
-        <v>-0.0765</v>
-      </c>
-      <c r="E27">
-        <v>0.0551</v>
-      </c>
       <c r="G27">
-        <v>0.5736607142857142</v>
+        <v>0.5613496932515338</v>
       </c>
       <c r="H27">
-        <v>0.5736607142857142</v>
+        <v>0.5613496932515338</v>
       </c>
       <c r="I27">
-        <v>0.3950892857142857</v>
+        <v>0.392638036809816</v>
       </c>
       <c r="J27">
-        <v>0.3300982671174979</v>
+        <v>0.2811288343558282</v>
       </c>
       <c r="K27">
-        <v>1.41</v>
+        <v>0.894</v>
       </c>
       <c r="L27">
-        <v>0.3147321428571428</v>
+        <v>0.2742331288343559</v>
       </c>
       <c r="M27">
-        <v>0.761</v>
+        <v>0.867</v>
       </c>
       <c r="N27">
-        <v>0.03843434343434343</v>
+        <v>0.02969178082191781</v>
       </c>
       <c r="O27">
-        <v>0.5397163120567376</v>
+        <v>0.9697986577181208</v>
       </c>
       <c r="P27">
-        <v>0.761</v>
+        <v>0.867</v>
       </c>
       <c r="Q27">
-        <v>0.03843434343434343</v>
+        <v>0.02969178082191781</v>
       </c>
       <c r="R27">
-        <v>0.5397163120567376</v>
+        <v>0.9697986577181208</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3761,31 +3743,31 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>9.119999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="V27">
-        <v>0.4606060606060606</v>
+        <v>0.4417808219178083</v>
       </c>
       <c r="W27">
-        <v>0.06409090909090909</v>
+        <v>0.0423696682464455</v>
       </c>
       <c r="X27">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y27">
-        <v>-0.05868253631577199</v>
+        <v>-0.07027837859717725</v>
       </c>
       <c r="Z27">
-        <v>0.4480000000000001</v>
+        <v>0.5258064516129031</v>
       </c>
       <c r="AA27">
-        <v>0.1478840236686391</v>
+        <v>0.1478193548387096</v>
       </c>
       <c r="AB27">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC27">
-        <v>0.02511057826195799</v>
+        <v>0.0351713079950869</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -3797,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>-9.119999999999999</v>
+        <v>-12.9</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -3806,22 +3788,28 @@
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>-0.8539325842696627</v>
+        <v>-0.7914110429447855</v>
       </c>
       <c r="AK27">
-        <v>-0.9230769230769229</v>
+        <v>-1.954545454545455</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AN27">
         <v>0</v>
       </c>
+      <c r="AO27">
+        <v>106.6666666666667</v>
+      </c>
       <c r="AP27">
-        <v>-5.094972067039105</v>
+        <v>-9.772727272727273</v>
+      </c>
+      <c r="AQ27">
+        <v>106.6666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -3832,7 +3820,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Paramount Insurance Company Limited (DSE:PARAMOUNT)</t>
+          <t>Sonar Bangla Insurance Limited (DSE:SONARBAINS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3840,47 +3828,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D28">
-        <v>0.198</v>
-      </c>
-      <c r="E28">
-        <v>0.199</v>
-      </c>
       <c r="G28">
-        <v>0.6085714285714285</v>
+        <v>0.4253246753246753</v>
       </c>
       <c r="H28">
-        <v>0.6085714285714285</v>
+        <v>0.4253246753246753</v>
       </c>
       <c r="I28">
-        <v>0.3428571428571429</v>
+        <v>0.2886363636363636</v>
       </c>
       <c r="J28">
-        <v>0.2251428571428572</v>
+        <v>0.2098877728810085</v>
       </c>
       <c r="K28">
-        <v>0.787</v>
+        <v>0.666</v>
       </c>
       <c r="L28">
-        <v>0.2248571428571429</v>
+        <v>0.2162337662337663</v>
       </c>
       <c r="M28">
-        <v>0.404</v>
+        <v>0.401</v>
       </c>
       <c r="N28">
-        <v>0.02295454545454545</v>
+        <v>0.02331395348837209</v>
       </c>
       <c r="O28">
-        <v>0.5133418043202033</v>
+        <v>0.6021021021021021</v>
       </c>
       <c r="P28">
-        <v>0.404</v>
+        <v>0.401</v>
       </c>
       <c r="Q28">
-        <v>0.02295454545454545</v>
+        <v>0.02331395348837209</v>
       </c>
       <c r="R28">
-        <v>0.5133418043202033</v>
+        <v>0.6021021021021021</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3889,55 +3871,55 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>5.74</v>
+        <v>4.67</v>
       </c>
       <c r="V28">
-        <v>0.3261363636363636</v>
+        <v>0.2715116279069767</v>
       </c>
       <c r="W28">
-        <v>0.06450819672131149</v>
+        <v>0.06686746987951807</v>
       </c>
       <c r="X28">
-        <v>0.1227734454066811</v>
+        <v>0.1130988634086565</v>
       </c>
       <c r="Y28">
-        <v>-0.05826524868536959</v>
+        <v>-0.04623139352913841</v>
       </c>
       <c r="Z28">
-        <v>0.5681818181818182</v>
+        <v>0.6388716034017838</v>
       </c>
       <c r="AA28">
-        <v>0.1279220779220779</v>
+        <v>0.1340913379949193</v>
       </c>
       <c r="AB28">
-        <v>0.1227734454066811</v>
+        <v>0.1127417744759741</v>
       </c>
       <c r="AC28">
-        <v>0.005148632515396864</v>
+        <v>0.02134956351894529</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AG28">
-        <v>-5.74</v>
+        <v>-4.52</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>0.008645533141210375</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>0.01538461538461538</v>
       </c>
       <c r="AJ28">
-        <v>-0.4839797639123102</v>
+        <v>-0.3564668769716088</v>
       </c>
       <c r="AK28">
-        <v>-1.205882352941177</v>
+        <v>-0.8897637795275589</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3946,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>0.1587301587301587</v>
       </c>
       <c r="AP28">
-        <v>-4.592000000000001</v>
+        <v>-4.783068783068783</v>
       </c>
     </row>
     <row r="29">
@@ -3960,7 +3942,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Green Delta Insurance Company Limited (DSE:GREENDELT)</t>
+          <t>Crystal Insurance Company Limited (DSE:CRYSTALINS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3968,47 +3950,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D29">
-        <v>0.0473</v>
-      </c>
-      <c r="E29">
-        <v>0.278</v>
-      </c>
       <c r="G29">
-        <v>0.5778546712802768</v>
+        <v>0.3202357563850687</v>
       </c>
       <c r="H29">
-        <v>0.5778546712802768</v>
+        <v>0.3202357563850687</v>
       </c>
       <c r="I29">
-        <v>0.3910034602076125</v>
+        <v>0.2475442043222004</v>
       </c>
       <c r="J29">
-        <v>0.2560320734628693</v>
+        <v>0.2279469548133595</v>
       </c>
       <c r="K29">
-        <v>6.82</v>
+        <v>1.11</v>
       </c>
       <c r="L29">
-        <v>0.2359861591695502</v>
+        <v>0.2180746561886051</v>
       </c>
       <c r="M29">
-        <v>3.39</v>
+        <v>0.312</v>
       </c>
       <c r="N29">
-        <v>0.05347003154574133</v>
+        <v>0.009149560117302053</v>
       </c>
       <c r="O29">
-        <v>0.4970674486803519</v>
+        <v>0.281081081081081</v>
       </c>
       <c r="P29">
-        <v>3.39</v>
+        <v>0.312</v>
       </c>
       <c r="Q29">
-        <v>0.05347003154574133</v>
+        <v>0.009149560117302053</v>
       </c>
       <c r="R29">
-        <v>0.4970674486803519</v>
+        <v>0.281081081081081</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4017,67 +3993,73 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>16.4</v>
+        <v>0.336</v>
       </c>
       <c r="V29">
-        <v>0.2586750788643533</v>
+        <v>0.009853372434017595</v>
       </c>
       <c r="W29">
-        <v>0.08399014778325123</v>
+        <v>0.1178343949044586</v>
       </c>
       <c r="X29">
-        <v>0.1227734454066811</v>
+        <v>0.112820864267028</v>
       </c>
       <c r="Y29">
-        <v>-0.03878329762342984</v>
+        <v>0.005013530637430569</v>
       </c>
       <c r="Z29">
-        <v>0.4594594594594594</v>
+        <v>0.5584201865057598</v>
       </c>
       <c r="AA29">
-        <v>0.1176363580775345</v>
+        <v>0.1272901810202962</v>
       </c>
       <c r="AB29">
-        <v>0.1227734454066811</v>
+        <v>0.1126841692660283</v>
       </c>
       <c r="AC29">
-        <v>-0.005137087329146528</v>
+        <v>0.01460601175426789</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AG29">
-        <v>-16.4</v>
+        <v>-0.222</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>0.003331969369264044</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>0.01226597805035507</v>
       </c>
       <c r="AJ29">
-        <v>-0.3489361702127659</v>
+        <v>-0.006552925202196116</v>
       </c>
       <c r="AK29">
-        <v>-0.3241106719367589</v>
+        <v>-0.02478231748158071</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>0.07037037037037037</v>
+      </c>
+      <c r="AO29">
+        <v>66.31578947368422</v>
       </c>
       <c r="AP29">
-        <v>-1.378151260504201</v>
+        <v>-0.137037037037037</v>
+      </c>
+      <c r="AQ29">
+        <v>66.31578947368422</v>
       </c>
     </row>
     <row r="30">
@@ -4088,7 +4070,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eastland Insurance Company Limited (DSE:EASTLAND)</t>
+          <t>Green Delta Insurance Company Limited (DSE:GREENDELT)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4097,46 +4079,46 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0246</v>
+        <v>0.0345</v>
       </c>
       <c r="E30">
-        <v>-0.0358</v>
+        <v>0.176</v>
       </c>
       <c r="G30">
-        <v>0.3232758620689655</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="H30">
-        <v>0.3232758620689655</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="I30">
-        <v>0.3089080459770115</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="J30">
-        <v>0.2346312798656851</v>
+        <v>0.2308354866494401</v>
       </c>
       <c r="K30">
-        <v>1.35</v>
+        <v>5.37</v>
       </c>
       <c r="L30">
-        <v>0.1939655172413793</v>
+        <v>0.1988888888888889</v>
       </c>
       <c r="M30">
-        <v>0.806</v>
+        <v>2.28</v>
       </c>
       <c r="N30">
-        <v>0.04050251256281408</v>
+        <v>0.03689320388349514</v>
       </c>
       <c r="O30">
-        <v>0.597037037037037</v>
+        <v>0.4245810055865921</v>
       </c>
       <c r="P30">
-        <v>0.806</v>
+        <v>2.28</v>
       </c>
       <c r="Q30">
-        <v>0.04050251256281408</v>
+        <v>0.03689320388349514</v>
       </c>
       <c r="R30">
-        <v>0.597037037037037</v>
+        <v>0.4245810055865921</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4145,31 +4127,31 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>4.37</v>
+        <v>16.5</v>
       </c>
       <c r="V30">
-        <v>0.2195979899497488</v>
+        <v>0.2669902912621359</v>
       </c>
       <c r="W30">
-        <v>0.0574468085106383</v>
+        <v>0.08014925373134328</v>
       </c>
       <c r="X30">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y30">
-        <v>-0.06532663689604276</v>
+        <v>-0.03249879311227946</v>
       </c>
       <c r="Z30">
-        <v>0.3873121869782972</v>
+        <v>0.5335968379446641</v>
       </c>
       <c r="AA30">
-        <v>0.09087555413829541</v>
+        <v>0.1231730857615589</v>
       </c>
       <c r="AB30">
-        <v>0.1227734454066811</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC30">
-        <v>-0.03189789126838566</v>
+        <v>0.0105250389179362</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -4181,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>-4.37</v>
+        <v>-16.5</v>
       </c>
       <c r="AH30">
         <v>0</v>
@@ -4190,28 +4172,22 @@
         <v>0</v>
       </c>
       <c r="AJ30">
-        <v>-0.2813908564069543</v>
+        <v>-0.3642384105960265</v>
       </c>
       <c r="AK30">
-        <v>-0.3328255902513328</v>
+        <v>-0.3444676409185803</v>
       </c>
       <c r="AL30">
-        <v>0.348</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>0.348</v>
+        <v>0</v>
       </c>
       <c r="AN30">
         <v>0</v>
       </c>
-      <c r="AO30">
-        <v>6.17816091954023</v>
-      </c>
       <c r="AP30">
-        <v>-2.071090047393365</v>
-      </c>
-      <c r="AQ30">
-        <v>6.17816091954023</v>
+        <v>-1.556603773584906</v>
       </c>
     </row>
     <row r="31">
@@ -4222,7 +4198,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Republic Insurance Company Limited (DSE:REPUBLIC)</t>
+          <t>Paramount Insurance Company Limited (DSE:PARAMOUNT)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4231,46 +4207,46 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.04940000000000001</v>
+        <v>0.142</v>
       </c>
       <c r="E31">
-        <v>0.0447</v>
+        <v>0.0295</v>
       </c>
       <c r="G31">
-        <v>0.2948207171314741</v>
+        <v>0.3614035087719298</v>
       </c>
       <c r="H31">
-        <v>0.2948207171314741</v>
+        <v>0.3614035087719298</v>
       </c>
       <c r="I31">
-        <v>0.2290836653386454</v>
+        <v>0.196140350877193</v>
       </c>
       <c r="J31">
-        <v>0.1469164663659412</v>
+        <v>0.1582576477294319</v>
       </c>
       <c r="K31">
-        <v>0.775</v>
+        <v>0.447</v>
       </c>
       <c r="L31">
-        <v>0.1543824701195219</v>
+        <v>0.1568421052631579</v>
       </c>
       <c r="M31">
-        <v>0.462</v>
+        <v>0.37</v>
       </c>
       <c r="N31">
-        <v>0.02733727810650888</v>
+        <v>0.01651785714285714</v>
       </c>
       <c r="O31">
-        <v>0.5961290322580646</v>
+        <v>0.8277404921700223</v>
       </c>
       <c r="P31">
-        <v>0.462</v>
+        <v>0.37</v>
       </c>
       <c r="Q31">
-        <v>0.02733727810650888</v>
+        <v>0.01651785714285714</v>
       </c>
       <c r="R31">
-        <v>0.5961290322580646</v>
+        <v>0.8277404921700223</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -4279,61 +4255,67 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>0.736</v>
+        <v>4.38</v>
       </c>
       <c r="V31">
-        <v>0.04355029585798817</v>
+        <v>0.1955357142857143</v>
       </c>
       <c r="W31">
-        <v>0.08115183246073299</v>
+        <v>0.04257142857142857</v>
       </c>
       <c r="X31">
-        <v>0.1232161693111624</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y31">
-        <v>-0.04206433685042946</v>
+        <v>-0.07007661827219416</v>
       </c>
       <c r="Z31">
-        <v>0.5733211512105983</v>
+        <v>0.5987394957983194</v>
       </c>
       <c r="AA31">
-        <v>0.08423031762871455</v>
+        <v>0.09475510420774809</v>
       </c>
       <c r="AB31">
-        <v>0.1227990365750236</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC31">
-        <v>-0.03856871894630901</v>
+        <v>-0.01789294263587465</v>
       </c>
       <c r="AD31">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>-0.604</v>
+        <v>-4.38</v>
       </c>
       <c r="AH31">
-        <v>0.007750117426021607</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>0.01487826871055005</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>-0.03706431026018655</v>
+        <v>-0.2430632630410655</v>
       </c>
       <c r="AK31">
-        <v>-0.07423795476892821</v>
+        <v>-0.8295454545454545</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
         <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>-7.239669421487603</v>
       </c>
     </row>
     <row r="32">
@@ -4344,7 +4326,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agrani Insurance Company Limited (DSE:AGRANINS)</t>
+          <t>Eastland Insurance Company Limited (DSE:EASTLAND)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4353,46 +4335,46 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.0125</v>
+        <v>-0.0239</v>
       </c>
       <c r="E32">
-        <v>-0.096</v>
+        <v>-0.0524</v>
       </c>
       <c r="G32">
-        <v>0.2384905660377359</v>
+        <v>0.2516556291390729</v>
       </c>
       <c r="H32">
-        <v>0.2384905660377359</v>
+        <v>0.2516556291390729</v>
       </c>
       <c r="I32">
-        <v>0.2116981132075472</v>
+        <v>0.1609271523178808</v>
       </c>
       <c r="J32">
-        <v>0.1123145312654351</v>
+        <v>0.1609271523178808</v>
       </c>
       <c r="K32">
-        <v>0.36</v>
+        <v>1.1</v>
       </c>
       <c r="L32">
-        <v>0.1358490566037736</v>
+        <v>0.1821192052980133</v>
       </c>
       <c r="M32">
-        <v>0.204</v>
+        <v>0.013</v>
       </c>
       <c r="N32">
-        <v>0.01789473684210526</v>
+        <v>0.0006770833333333334</v>
       </c>
       <c r="O32">
-        <v>0.5666666666666667</v>
+        <v>0.01181818181818182</v>
       </c>
       <c r="P32">
-        <v>0.204</v>
+        <v>0.013</v>
       </c>
       <c r="Q32">
-        <v>0.01789473684210526</v>
+        <v>0.0006770833333333334</v>
       </c>
       <c r="R32">
-        <v>0.5666666666666667</v>
+        <v>0.01181818181818182</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -4401,67 +4383,73 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>3.87</v>
+        <v>3.41</v>
       </c>
       <c r="V32">
-        <v>0.3394736842105263</v>
+        <v>0.1776041666666667</v>
       </c>
       <c r="W32">
-        <v>0.05564142194744977</v>
+        <v>0.06285714285714286</v>
       </c>
       <c r="X32">
-        <v>0.1242998837596986</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y32">
-        <v>-0.06865846181224881</v>
+        <v>-0.04979090398647988</v>
       </c>
       <c r="Z32">
-        <v>0.7391910739191075</v>
+        <v>0.4600152322924601</v>
       </c>
       <c r="AA32">
-        <v>0.0830218989828182</v>
+        <v>0.07402894135567403</v>
       </c>
       <c r="AB32">
-        <v>0.1228600367721276</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC32">
-        <v>-0.03983813778930941</v>
+        <v>-0.03861910548794871</v>
       </c>
       <c r="AD32">
-        <v>0.307</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>0.307</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>-3.563</v>
+        <v>-3.41</v>
       </c>
       <c r="AH32">
-        <v>0.02622362688989493</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>0.03967946232389815</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>-0.4546382544340947</v>
+        <v>-0.2159594680177328</v>
       </c>
       <c r="AK32">
-        <v>-0.9213860874062583</v>
+        <v>-0.2645461598138091</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN32">
-        <v>0.4857594936708861</v>
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>9.719999999999999</v>
       </c>
       <c r="AP32">
-        <v>-5.637658227848101</v>
+        <v>-3.714596949891067</v>
+      </c>
+      <c r="AQ32">
+        <v>9.719999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -4472,7 +4460,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nitol Insurance Company Limited (DSE:NITOLINS)</t>
+          <t>Asia Insurance Limited (DSE:ASIAINS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4481,46 +4469,46 @@
         </is>
       </c>
       <c r="D33">
-        <v>-0.0556</v>
+        <v>-0.0106</v>
       </c>
       <c r="E33">
-        <v>-0.0239</v>
+        <v>0.0192</v>
       </c>
       <c r="G33">
-        <v>0.4605263157894737</v>
+        <v>0.3100616016427105</v>
       </c>
       <c r="H33">
-        <v>0.4605263157894737</v>
+        <v>0.3100616016427105</v>
       </c>
       <c r="I33">
-        <v>0.2368421052631579</v>
+        <v>0.2525667351129363</v>
       </c>
       <c r="J33">
-        <v>0.1988169966199904</v>
+        <v>0.1466584991286042</v>
       </c>
       <c r="K33">
-        <v>0.91</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L33">
-        <v>0.199561403508772</v>
+        <v>0.1410677618069815</v>
       </c>
       <c r="M33">
-        <v>0.527</v>
+        <v>0.459</v>
       </c>
       <c r="N33">
-        <v>0.03233128834355829</v>
+        <v>0.0211520737327189</v>
       </c>
       <c r="O33">
-        <v>0.5791208791208792</v>
+        <v>0.6681222707423581</v>
       </c>
       <c r="P33">
-        <v>0.527</v>
+        <v>0.459</v>
       </c>
       <c r="Q33">
-        <v>0.03233128834355829</v>
+        <v>0.0211520737327189</v>
       </c>
       <c r="R33">
-        <v>0.5791208791208792</v>
+        <v>0.6681222707423581</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -4529,67 +4517,73 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>0.225</v>
+        <v>0.221</v>
       </c>
       <c r="V33">
-        <v>0.01380368098159509</v>
+        <v>0.01018433179723502</v>
       </c>
       <c r="W33">
-        <v>0.06791044776119404</v>
+        <v>0.06079646017699115</v>
       </c>
       <c r="X33">
-        <v>0.1227734454066811</v>
+        <v>0.1128195648879047</v>
       </c>
       <c r="Y33">
-        <v>-0.05486299764548704</v>
+        <v>-0.05202310471091355</v>
       </c>
       <c r="Z33">
-        <v>0.3566679702776691</v>
+        <v>0.500565320176791</v>
       </c>
       <c r="AA33">
-        <v>0.07091165464115416</v>
+        <v>0.07341215857295738</v>
       </c>
       <c r="AB33">
-        <v>0.1227734454066811</v>
+        <v>0.1126777200992824</v>
       </c>
       <c r="AC33">
-        <v>-0.05186179076552691</v>
+        <v>-0.03926556152632502</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AG33">
-        <v>-0.225</v>
+        <v>-0.149</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>0.003306999816277788</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>0.00681044267877412</v>
       </c>
       <c r="AJ33">
-        <v>-0.01399688958009331</v>
+        <v>-0.006913832304765442</v>
       </c>
       <c r="AK33">
-        <v>-0.0196078431372549</v>
+        <v>-0.01439474446913342</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>0.05333333333333332</v>
+      </c>
+      <c r="AO33">
+        <v>58.57142857142857</v>
       </c>
       <c r="AP33">
-        <v>-0.1785714285714286</v>
+        <v>-0.1103703703703704</v>
+      </c>
+      <c r="AQ33">
+        <v>58.57142857142857</v>
       </c>
     </row>
     <row r="34">
@@ -4609,46 +4603,46 @@
         </is>
       </c>
       <c r="D34">
-        <v>-0.0452</v>
+        <v>-0.0747</v>
       </c>
       <c r="E34">
-        <v>-0.0484</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="G34">
-        <v>0.3371040723981901</v>
+        <v>0.2882205513784461</v>
       </c>
       <c r="H34">
-        <v>0.3371040723981901</v>
+        <v>0.2882205513784461</v>
       </c>
       <c r="I34">
-        <v>0.2398190045248869</v>
+        <v>0.2087719298245614</v>
       </c>
       <c r="J34">
-        <v>0.1859147328656233</v>
+        <v>0.1668177621086208</v>
       </c>
       <c r="K34">
-        <v>0.845</v>
+        <v>0.667</v>
       </c>
       <c r="L34">
-        <v>0.1911764705882353</v>
+        <v>0.1671679197994987</v>
       </c>
       <c r="M34">
-        <v>0.607</v>
+        <v>0.542</v>
       </c>
       <c r="N34">
-        <v>0.04073825503355705</v>
+        <v>0.03927536231884058</v>
       </c>
       <c r="O34">
-        <v>0.7183431952662722</v>
+        <v>0.8125937031484258</v>
       </c>
       <c r="P34">
-        <v>0.607</v>
+        <v>0.542</v>
       </c>
       <c r="Q34">
-        <v>0.04073825503355705</v>
+        <v>0.03927536231884058</v>
       </c>
       <c r="R34">
-        <v>0.7183431952662722</v>
+        <v>0.8125937031484258</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -4657,55 +4651,55 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>5.02</v>
+        <v>4.33</v>
       </c>
       <c r="V34">
-        <v>0.3369127516778523</v>
+        <v>0.313768115942029</v>
       </c>
       <c r="W34">
-        <v>0.04246231155778895</v>
+        <v>0.04476510067114094</v>
       </c>
       <c r="X34">
-        <v>0.1227734454066811</v>
+        <v>0.1133672626041867</v>
       </c>
       <c r="Y34">
-        <v>-0.08031113384889213</v>
+        <v>-0.06860216193304577</v>
       </c>
       <c r="Z34">
-        <v>0.3012951601908657</v>
+        <v>0.4038461538461539</v>
       </c>
       <c r="AA34">
-        <v>0.05601520922058999</v>
+        <v>0.06736871162078917</v>
       </c>
       <c r="AB34">
-        <v>0.1227734454066811</v>
+        <v>0.1127968106557481</v>
       </c>
       <c r="AC34">
-        <v>-0.06675823618609109</v>
+        <v>-0.04542809903495894</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AG34">
-        <v>-5.02</v>
+        <v>-4.138</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>0.0137221269296741</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>0.01412595644496763</v>
       </c>
       <c r="AJ34">
-        <v>-0.5080971659919028</v>
+        <v>-0.4282757193127716</v>
       </c>
       <c r="AK34">
-        <v>-0.5080971659919028</v>
+        <v>-0.4467717555603541</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -4714,10 +4708,10 @@
         <v>0</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>0.2018927444794953</v>
       </c>
       <c r="AP34">
-        <v>-4.183333333333334</v>
+        <v>-4.351209253417456</v>
       </c>
     </row>
     <row r="35">
@@ -4728,7 +4722,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dhaka Insurance Limited (DSE:DHAKAINS)</t>
+          <t>Central Insurance Company Limited (DSE:CENTRALINS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4737,46 +4731,46 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.113</v>
+        <v>0.0604</v>
       </c>
       <c r="E35">
-        <v>-0.197</v>
+        <v>0.137</v>
       </c>
       <c r="G35">
-        <v>0.3387096774193549</v>
+        <v>0.3611738148984199</v>
       </c>
       <c r="H35">
-        <v>0.3387096774193549</v>
+        <v>0.3611738148984199</v>
       </c>
       <c r="I35">
-        <v>0.2078341013824885</v>
+        <v>0.2776523702031603</v>
       </c>
       <c r="J35">
-        <v>0.1039170506912442</v>
+        <v>0.2776523702031603</v>
       </c>
       <c r="K35">
-        <v>0.237</v>
+        <v>1.52</v>
       </c>
       <c r="L35">
-        <v>0.05460829493087557</v>
+        <v>0.3431151241534989</v>
       </c>
       <c r="M35">
-        <v>1.01</v>
+        <v>0.753</v>
       </c>
       <c r="N35">
-        <v>0.05401069518716578</v>
+        <v>0.04114754098360655</v>
       </c>
       <c r="O35">
-        <v>4.261603375527426</v>
+        <v>0.4953947368421053</v>
       </c>
       <c r="P35">
-        <v>1.01</v>
+        <v>0.753</v>
       </c>
       <c r="Q35">
-        <v>0.05401069518716578</v>
+        <v>0.04114754098360655</v>
       </c>
       <c r="R35">
-        <v>4.261603375527426</v>
+        <v>0.4953947368421053</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -4785,73 +4779,67 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>6.6</v>
+        <v>7.02</v>
       </c>
       <c r="V35">
-        <v>0.3529411764705882</v>
+        <v>0.3836065573770491</v>
       </c>
       <c r="W35">
-        <v>0.01529032258064516</v>
+        <v>0.0582375478927203</v>
       </c>
       <c r="X35">
-        <v>0.1228401302015628</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y35">
-        <v>-0.1075498076209177</v>
+        <v>-0.05441049895090244</v>
       </c>
       <c r="Z35">
-        <v>0.5205709487825357</v>
+        <v>0.240368963646229</v>
       </c>
       <c r="AA35">
-        <v>0.05409619767302387</v>
+        <v>0.06673901247965273</v>
       </c>
       <c r="AB35">
-        <v>0.122777325590237</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC35">
-        <v>-0.06868112791721316</v>
+        <v>-0.04590903436397001</v>
       </c>
       <c r="AD35">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>-6.577999999999999</v>
+        <v>-7.02</v>
       </c>
       <c r="AH35">
-        <v>0.001175088131609871</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>0.001651403693139168</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>-0.542649727767695</v>
+        <v>-0.6223404255319148</v>
       </c>
       <c r="AK35">
-        <v>-0.9785778042249328</v>
+        <v>-0.4134275618374558</v>
       </c>
       <c r="AL35">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>0.0205607476635514</v>
-      </c>
-      <c r="AO35">
-        <v>225.5</v>
+        <v>0</v>
       </c>
       <c r="AP35">
-        <v>-6.147663551401868</v>
-      </c>
-      <c r="AQ35">
-        <v>225.5</v>
+        <v>-5.086956521739131</v>
       </c>
     </row>
     <row r="36">
@@ -4862,7 +4850,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Union Insurance Co. Ltd. (DSE:UNIONINS)</t>
+          <t>Nitol Insurance Company Limited (DSE:NITOLINS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4870,41 +4858,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D36">
+        <v>-0.0582</v>
+      </c>
+      <c r="E36">
+        <v>-0.068</v>
+      </c>
       <c r="G36">
-        <v>0.1641791044776119</v>
+        <v>0.2818791946308725</v>
       </c>
       <c r="H36">
-        <v>0.1641791044776119</v>
+        <v>0.2818791946308725</v>
       </c>
       <c r="I36">
-        <v>-0.002487562189054726</v>
+        <v>0.2042505592841163</v>
       </c>
       <c r="J36">
-        <v>-0.002487562189054726</v>
+        <v>0.1595078299776286</v>
       </c>
       <c r="K36">
-        <v>-0.008</v>
+        <v>0.713</v>
       </c>
       <c r="L36">
-        <v>-0.001326699834162521</v>
+        <v>0.1595078299776286</v>
       </c>
       <c r="M36">
-        <v>0.242</v>
+        <v>0.399</v>
       </c>
       <c r="N36">
-        <v>0.01375</v>
+        <v>0.02809859154929578</v>
       </c>
       <c r="O36">
-        <v>-30.25</v>
+        <v>0.5596072931276298</v>
       </c>
       <c r="P36">
-        <v>0.242</v>
+        <v>0.399</v>
       </c>
       <c r="Q36">
-        <v>0.01375</v>
+        <v>0.02809859154929578</v>
       </c>
       <c r="R36">
-        <v>-30.25</v>
+        <v>0.5596072931276298</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -4913,73 +4907,329 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>2.83</v>
+        <v>0.186</v>
       </c>
       <c r="V36">
-        <v>0.1607954545454545</v>
+        <v>0.01309859154929578</v>
       </c>
       <c r="W36">
-        <v>-0.001342281879194631</v>
+        <v>0.06094017094017094</v>
       </c>
       <c r="X36">
-        <v>0.1234014570402978</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y36">
-        <v>-0.1247437389194924</v>
+        <v>-0.0517078759034518</v>
       </c>
       <c r="Z36">
-        <v>1.563391236712471</v>
+        <v>0.3895424836601307</v>
       </c>
       <c r="AA36">
-        <v>-0.00388903292714545</v>
+        <v>0.06213507625272332</v>
       </c>
       <c r="AB36">
-        <v>0.1228096295629157</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC36">
-        <v>-0.1266986624900612</v>
+        <v>-0.05051297059089942</v>
       </c>
       <c r="AD36">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>-2.635</v>
+        <v>-0.186</v>
       </c>
       <c r="AH36">
-        <v>0.01095813430738972</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>0.02245250431778929</v>
+        <v>0</v>
       </c>
       <c r="AJ36">
-        <v>-0.1760775141997995</v>
+        <v>-0.01327244184387042</v>
       </c>
       <c r="AK36">
-        <v>-0.4500426985482494</v>
+        <v>-0.01719992602182356</v>
       </c>
       <c r="AL36">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AN36">
-        <v>0.7442748091603053</v>
-      </c>
-      <c r="AO36">
-        <v>-0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AP36">
-        <v>-10.05725190839695</v>
-      </c>
-      <c r="AQ36">
-        <v>-0.3333333333333333</v>
+        <v>-0.1690909090909091</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dhaka Insurance Limited (DSE:DHAKAINS)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.107</v>
+      </c>
+      <c r="E37">
+        <v>-0.207</v>
+      </c>
+      <c r="G37">
+        <v>0.2058111380145279</v>
+      </c>
+      <c r="H37">
+        <v>0.2058111380145279</v>
+      </c>
+      <c r="I37">
+        <v>0.1774818401937046</v>
+      </c>
+      <c r="J37">
+        <v>0.0887409200968523</v>
+      </c>
+      <c r="K37">
+        <v>0.224</v>
+      </c>
+      <c r="L37">
+        <v>0.05423728813559323</v>
+      </c>
+      <c r="M37">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="N37">
+        <v>0.04829015544041451</v>
+      </c>
+      <c r="O37">
+        <v>4.160714285714286</v>
+      </c>
+      <c r="P37">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="Q37">
+        <v>0.04829015544041451</v>
+      </c>
+      <c r="R37">
+        <v>4.160714285714286</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0.899</v>
+      </c>
+      <c r="V37">
+        <v>0.04658031088082901</v>
+      </c>
+      <c r="W37">
+        <v>0.016</v>
+      </c>
+      <c r="X37">
+        <v>0.1128007171580818</v>
+      </c>
+      <c r="Y37">
+        <v>-0.09680071715808182</v>
+      </c>
+      <c r="Z37">
+        <v>0.5850687066156679</v>
+      </c>
+      <c r="AA37">
+        <v>0.05191953534494971</v>
+      </c>
+      <c r="AB37">
+        <v>0.1126799705032855</v>
+      </c>
+      <c r="AC37">
+        <v>-0.06076043515833579</v>
+      </c>
+      <c r="AD37">
+        <v>0.057</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0.057</v>
+      </c>
+      <c r="AG37">
+        <v>-0.842</v>
+      </c>
+      <c r="AH37">
+        <v>0.00294467117838508</v>
+      </c>
+      <c r="AI37">
+        <v>0.004299615297578638</v>
+      </c>
+      <c r="AJ37">
+        <v>-0.04561707660634955</v>
+      </c>
+      <c r="AK37">
+        <v>-0.06813400226573879</v>
+      </c>
+      <c r="AL37">
+        <v>0.005</v>
+      </c>
+      <c r="AM37">
+        <v>0.005</v>
+      </c>
+      <c r="AN37">
+        <v>0.06499429874572406</v>
+      </c>
+      <c r="AO37">
+        <v>146.6</v>
+      </c>
+      <c r="AP37">
+        <v>-0.960091220068415</v>
+      </c>
+      <c r="AQ37">
+        <v>146.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Rupali Insurance Company Limited (DSE:RUPALIINS)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>-0.09880000000000001</v>
+      </c>
+      <c r="E38">
+        <v>-0.173</v>
+      </c>
+      <c r="G38">
+        <v>0.2484126984126984</v>
+      </c>
+      <c r="H38">
+        <v>0.2484126984126984</v>
+      </c>
+      <c r="I38">
+        <v>0.1103174603174603</v>
+      </c>
+      <c r="J38">
+        <v>0.1103174603174603</v>
+      </c>
+      <c r="K38">
+        <v>0.468</v>
+      </c>
+      <c r="L38">
+        <v>0.1238095238095238</v>
+      </c>
+      <c r="M38">
+        <v>0.572</v>
+      </c>
+      <c r="N38">
+        <v>0.02763285024154589</v>
+      </c>
+      <c r="O38">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="P38">
+        <v>0.572</v>
+      </c>
+      <c r="Q38">
+        <v>0.02763285024154589</v>
+      </c>
+      <c r="R38">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.3927536231884058</v>
+      </c>
+      <c r="W38">
+        <v>0.02463157894736842</v>
+      </c>
+      <c r="X38">
+        <v>0.1126480468436227</v>
+      </c>
+      <c r="Y38">
+        <v>-0.08801646789625432</v>
+      </c>
+      <c r="Z38">
+        <v>0.3825910931174089</v>
+      </c>
+      <c r="AA38">
+        <v>0.04220647773279352</v>
+      </c>
+      <c r="AB38">
+        <v>0.1126480468436227</v>
+      </c>
+      <c r="AC38">
+        <v>-0.07044156911082922</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>-0.6467780429594273</v>
+      </c>
+      <c r="AK38">
+        <v>-0.9270239452679593</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>-14.59605026929982</v>
       </c>
     </row>
   </sheetData>
